--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -1686,7 +1686,7 @@
         <v>113361342</v>
       </c>
       <c r="B11" t="n">
-        <v>90029</v>
+        <v>90045</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>113361143</v>
       </c>
       <c r="B12" t="n">
-        <v>79168</v>
+        <v>79184</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>113360892</v>
       </c>
       <c r="B13" t="n">
-        <v>90029</v>
+        <v>90045</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -1789,10 +1789,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113361143</v>
+        <v>113360892</v>
       </c>
       <c r="B12" t="n">
-        <v>79184</v>
+        <v>90045</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1805,21 +1805,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1828,14 +1828,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tågsjötorp (Backe), Ång</t>
+          <t>Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577603</v>
+        <v>577629</v>
       </c>
       <c r="R12" t="n">
-        <v>7078385</v>
+        <v>7078378</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1895,10 +1895,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113360892</v>
+        <v>113361143</v>
       </c>
       <c r="B13" t="n">
-        <v>90045</v>
+        <v>79184</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1911,21 +1911,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1934,14 +1934,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp (Backe), Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577629</v>
+        <v>577603</v>
       </c>
       <c r="R13" t="n">
-        <v>7078378</v>
+        <v>7078385</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113361342</v>
+        <v>113361143</v>
       </c>
       <c r="B11" t="n">
-        <v>90045</v>
+        <v>79196</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577519</v>
+        <v>577603</v>
       </c>
       <c r="R11" t="n">
-        <v>7078419</v>
+        <v>7078385</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1792,7 +1792,7 @@
         <v>113360892</v>
       </c>
       <c r="B12" t="n">
-        <v>90045</v>
+        <v>90057</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1895,10 +1895,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113361143</v>
+        <v>113361342</v>
       </c>
       <c r="B13" t="n">
-        <v>79184</v>
+        <v>90057</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1911,21 +1911,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1938,10 +1938,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577603</v>
+        <v>577519</v>
       </c>
       <c r="R13" t="n">
-        <v>7078385</v>
+        <v>7078419</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113361143</v>
+        <v>113360892</v>
       </c>
       <c r="B11" t="n">
-        <v>79196</v>
+        <v>90079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1722,14 +1722,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tågsjötorp (Backe), Ång</t>
+          <t>Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577603</v>
+        <v>577629</v>
       </c>
       <c r="R11" t="n">
-        <v>7078385</v>
+        <v>7078378</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1789,10 +1789,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113360892</v>
+        <v>113361342</v>
       </c>
       <c r="B12" t="n">
-        <v>90057</v>
+        <v>90079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1828,14 +1828,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp (Backe), Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577629</v>
+        <v>577519</v>
       </c>
       <c r="R12" t="n">
-        <v>7078378</v>
+        <v>7078419</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1895,10 +1895,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113361342</v>
+        <v>113361143</v>
       </c>
       <c r="B13" t="n">
-        <v>90057</v>
+        <v>79218</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1911,21 +1911,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1938,10 +1938,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577519</v>
+        <v>577603</v>
       </c>
       <c r="R13" t="n">
-        <v>7078419</v>
+        <v>7078385</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113360892</v>
+        <v>113361143</v>
       </c>
       <c r="B11" t="n">
-        <v>90079</v>
+        <v>79222</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1722,14 +1722,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp (Backe), Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577629</v>
+        <v>577603</v>
       </c>
       <c r="R11" t="n">
-        <v>7078378</v>
+        <v>7078385</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1792,7 +1792,7 @@
         <v>113361342</v>
       </c>
       <c r="B12" t="n">
-        <v>90079</v>
+        <v>90083</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1895,10 +1895,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113361143</v>
+        <v>113360892</v>
       </c>
       <c r="B13" t="n">
-        <v>79218</v>
+        <v>90083</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1911,21 +1911,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1934,14 +1934,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tågsjötorp (Backe), Ång</t>
+          <t>Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577603</v>
+        <v>577629</v>
       </c>
       <c r="R13" t="n">
-        <v>7078385</v>
+        <v>7078378</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113361143</v>
+        <v>113361342</v>
       </c>
       <c r="B11" t="n">
-        <v>79222</v>
+        <v>90083</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577603</v>
+        <v>577519</v>
       </c>
       <c r="R11" t="n">
-        <v>7078385</v>
+        <v>7078419</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1789,10 +1789,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113361342</v>
+        <v>113361143</v>
       </c>
       <c r="B12" t="n">
-        <v>90083</v>
+        <v>79222</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1805,21 +1805,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1832,10 +1832,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577519</v>
+        <v>577603</v>
       </c>
       <c r="R12" t="n">
-        <v>7078419</v>
+        <v>7078385</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113361342</v>
+        <v>113361143</v>
       </c>
       <c r="B11" t="n">
-        <v>90083</v>
+        <v>79228</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577519</v>
+        <v>577603</v>
       </c>
       <c r="R11" t="n">
-        <v>7078419</v>
+        <v>7078385</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1789,10 +1789,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113361143</v>
+        <v>113361342</v>
       </c>
       <c r="B12" t="n">
-        <v>79222</v>
+        <v>90089</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1805,21 +1805,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1832,10 +1832,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577603</v>
+        <v>577519</v>
       </c>
       <c r="R12" t="n">
-        <v>7078385</v>
+        <v>7078419</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1898,7 +1898,7 @@
         <v>113360892</v>
       </c>
       <c r="B13" t="n">
-        <v>90083</v>
+        <v>90089</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113361143</v>
+        <v>113361342</v>
       </c>
       <c r="B11" t="n">
-        <v>79228</v>
+        <v>90096</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577603</v>
+        <v>577519</v>
       </c>
       <c r="R11" t="n">
-        <v>7078385</v>
+        <v>7078419</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1789,10 +1789,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113361342</v>
+        <v>113360892</v>
       </c>
       <c r="B12" t="n">
-        <v>90089</v>
+        <v>90096</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1828,14 +1828,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tågsjötorp (Backe), Ång</t>
+          <t>Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577519</v>
+        <v>577629</v>
       </c>
       <c r="R12" t="n">
-        <v>7078419</v>
+        <v>7078378</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1895,10 +1895,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113360892</v>
+        <v>113361143</v>
       </c>
       <c r="B13" t="n">
-        <v>90089</v>
+        <v>79235</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1911,21 +1911,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1934,14 +1934,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp (Backe), Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577629</v>
+        <v>577603</v>
       </c>
       <c r="R13" t="n">
-        <v>7078378</v>
+        <v>7078385</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113361342</v>
+        <v>113361143</v>
       </c>
       <c r="B11" t="n">
-        <v>90096</v>
+        <v>79237</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577519</v>
+        <v>577603</v>
       </c>
       <c r="R11" t="n">
-        <v>7078419</v>
+        <v>7078385</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1792,7 +1792,7 @@
         <v>113360892</v>
       </c>
       <c r="B12" t="n">
-        <v>90096</v>
+        <v>90099</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1895,10 +1895,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113361143</v>
+        <v>113361342</v>
       </c>
       <c r="B13" t="n">
-        <v>79235</v>
+        <v>90099</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1911,21 +1911,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1938,10 +1938,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577603</v>
+        <v>577519</v>
       </c>
       <c r="R13" t="n">
-        <v>7078385</v>
+        <v>7078419</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113361143</v>
+        <v>113361342</v>
       </c>
       <c r="B11" t="n">
-        <v>79237</v>
+        <v>90130</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577603</v>
+        <v>577519</v>
       </c>
       <c r="R11" t="n">
-        <v>7078385</v>
+        <v>7078419</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1789,10 +1789,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113360892</v>
+        <v>113361143</v>
       </c>
       <c r="B12" t="n">
-        <v>90099</v>
+        <v>79265</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1805,21 +1805,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1828,14 +1828,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp (Backe), Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577629</v>
+        <v>577603</v>
       </c>
       <c r="R12" t="n">
-        <v>7078378</v>
+        <v>7078385</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1895,10 +1895,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113361342</v>
+        <v>113360892</v>
       </c>
       <c r="B13" t="n">
-        <v>90099</v>
+        <v>90130</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1934,14 +1934,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tågsjötorp (Backe), Ång</t>
+          <t>Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577519</v>
+        <v>577629</v>
       </c>
       <c r="R13" t="n">
-        <v>7078419</v>
+        <v>7078378</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113361342</v>
+        <v>113360892</v>
       </c>
       <c r="B11" t="n">
-        <v>90130</v>
+        <v>90131</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,14 +1722,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tågsjötorp (Backe), Ång</t>
+          <t>Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577519</v>
+        <v>577629</v>
       </c>
       <c r="R11" t="n">
-        <v>7078419</v>
+        <v>7078378</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1895,10 +1895,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113360892</v>
+        <v>113361342</v>
       </c>
       <c r="B13" t="n">
-        <v>90130</v>
+        <v>90131</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1934,14 +1934,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp (Backe), Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577629</v>
+        <v>577519</v>
       </c>
       <c r="R13" t="n">
-        <v>7078378</v>
+        <v>7078419</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -2001,10 +2001,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119873589</v>
+        <v>119872658</v>
       </c>
       <c r="B14" t="n">
-        <v>57463</v>
+        <v>90562</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2017,42 +2017,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577449</v>
+        <v>577509</v>
       </c>
       <c r="R14" t="n">
-        <v>7078490</v>
+        <v>7078448</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2096,22 +2091,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119872658</v>
+        <v>119873589</v>
       </c>
       <c r="B15" t="n">
-        <v>90562</v>
+        <v>57463</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2124,37 +2119,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577509</v>
+        <v>577449</v>
       </c>
       <c r="R15" t="n">
-        <v>7078448</v>
+        <v>7078490</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2198,12 +2198,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -3638,10 +3638,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119873315</v>
+        <v>119872304</v>
       </c>
       <c r="B30" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3654,34 +3654,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577459</v>
+        <v>577577</v>
       </c>
       <c r="R30" t="n">
-        <v>7078453</v>
+        <v>7078356</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3728,19 +3728,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119871541</v>
+        <v>119872102</v>
       </c>
       <c r="B31" t="n">
         <v>90562</v>
@@ -3776,17 +3776,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577611</v>
+        <v>577567</v>
       </c>
       <c r="R31" t="n">
-        <v>7078365</v>
+        <v>7078377</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3830,19 +3830,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119872304</v>
+        <v>119871122</v>
       </c>
       <c r="B32" t="n">
         <v>90562</v>
@@ -3882,10 +3882,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577577</v>
+        <v>577641</v>
       </c>
       <c r="R32" t="n">
-        <v>7078356</v>
+        <v>7078334</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3944,10 +3944,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119872102</v>
+        <v>119873315</v>
       </c>
       <c r="B33" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3960,37 +3960,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577567</v>
+        <v>577459</v>
       </c>
       <c r="R33" t="n">
-        <v>7078377</v>
+        <v>7078453</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4034,19 +4034,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119871122</v>
+        <v>119871541</v>
       </c>
       <c r="B34" t="n">
         <v>90562</v>
@@ -4082,14 +4082,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577641</v>
+        <v>577611</v>
       </c>
       <c r="R34" t="n">
-        <v>7078334</v>
+        <v>7078365</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4136,12 +4136,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4658,10 +4658,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119872285</v>
+        <v>119873574</v>
       </c>
       <c r="B40" t="n">
-        <v>90846</v>
+        <v>79643</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4670,38 +4670,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>6464</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577564</v>
+        <v>577449</v>
       </c>
       <c r="R40" t="n">
-        <v>7078366</v>
+        <v>7078503</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4862,10 +4862,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119873574</v>
+        <v>119872285</v>
       </c>
       <c r="B42" t="n">
-        <v>79643</v>
+        <v>90846</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4874,38 +4874,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6464</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577449</v>
+        <v>577564</v>
       </c>
       <c r="R42" t="n">
-        <v>7078503</v>
+        <v>7078366</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -2103,10 +2103,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119873589</v>
+        <v>119873713</v>
       </c>
       <c r="B15" t="n">
-        <v>57463</v>
+        <v>96862</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2115,46 +2115,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577449</v>
+        <v>577422</v>
       </c>
       <c r="R15" t="n">
-        <v>7078490</v>
+        <v>7078461</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2210,10 +2205,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119871553</v>
+        <v>119873728</v>
       </c>
       <c r="B16" t="n">
-        <v>79607</v>
+        <v>90580</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2226,21 +2221,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2250,10 +2245,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577606</v>
+        <v>577416</v>
       </c>
       <c r="R16" t="n">
-        <v>7078395</v>
+        <v>7078478</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2280,12 +2275,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2300,22 +2295,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119871000</v>
+        <v>119871569</v>
       </c>
       <c r="B17" t="n">
-        <v>90846</v>
+        <v>79636</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2324,41 +2319,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577653</v>
+        <v>577607</v>
       </c>
       <c r="R17" t="n">
-        <v>7078341</v>
+        <v>7078381</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2382,12 +2377,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2402,22 +2397,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119872661</v>
+        <v>119873866</v>
       </c>
       <c r="B18" t="n">
-        <v>90905</v>
+        <v>78526</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2426,25 +2421,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2454,10 +2449,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577523</v>
+        <v>577389</v>
       </c>
       <c r="R18" t="n">
-        <v>7078418</v>
+        <v>7078502</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2504,22 +2499,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119873866</v>
+        <v>119872671</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>90846</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2532,34 +2527,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>577389</v>
+        <v>577506</v>
       </c>
       <c r="R19" t="n">
-        <v>7078502</v>
+        <v>7078431</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2618,10 +2613,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119871910</v>
+        <v>119871099</v>
       </c>
       <c r="B20" t="n">
-        <v>78526</v>
+        <v>90846</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2634,34 +2629,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577581</v>
+        <v>577650</v>
       </c>
       <c r="R20" t="n">
-        <v>7078410</v>
+        <v>7078332</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2708,19 +2703,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119872671</v>
+        <v>119871033</v>
       </c>
       <c r="B21" t="n">
         <v>90846</v>
@@ -2756,14 +2751,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577506</v>
+        <v>577647</v>
       </c>
       <c r="R21" t="n">
-        <v>7078431</v>
+        <v>7078328</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2810,19 +2805,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119871327</v>
+        <v>119872102</v>
       </c>
       <c r="B22" t="n">
         <v>90562</v>
@@ -2858,17 +2853,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577636</v>
+        <v>577567</v>
       </c>
       <c r="R22" t="n">
-        <v>7078360</v>
+        <v>7078377</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2912,22 +2907,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119870839</v>
+        <v>119871327</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2940,21 +2935,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2964,10 +2959,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577741</v>
+        <v>577636</v>
       </c>
       <c r="R23" t="n">
-        <v>7078329</v>
+        <v>7078360</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3026,10 +3021,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119873602</v>
+        <v>119873511</v>
       </c>
       <c r="B24" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3042,21 +3037,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3066,10 +3061,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577440</v>
+        <v>577445</v>
       </c>
       <c r="R24" t="n">
-        <v>7078487</v>
+        <v>7078496</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3128,10 +3123,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119871569</v>
+        <v>119871122</v>
       </c>
       <c r="B25" t="n">
-        <v>79636</v>
+        <v>90562</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3140,25 +3135,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3168,13 +3163,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577607</v>
+        <v>577641</v>
       </c>
       <c r="R25" t="n">
-        <v>7078381</v>
+        <v>7078334</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3198,12 +3193,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3230,10 +3225,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119871920</v>
+        <v>119873574</v>
       </c>
       <c r="B26" t="n">
-        <v>90562</v>
+        <v>79643</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3242,25 +3237,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3270,10 +3265,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577561</v>
+        <v>577449</v>
       </c>
       <c r="R26" t="n">
-        <v>7078431</v>
+        <v>7078503</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3300,12 +3295,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3320,22 +3315,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119873018</v>
+        <v>119870839</v>
       </c>
       <c r="B27" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3348,34 +3343,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577513</v>
+        <v>577741</v>
       </c>
       <c r="R27" t="n">
-        <v>7078427</v>
+        <v>7078329</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3422,22 +3417,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119873511</v>
+        <v>119872661</v>
       </c>
       <c r="B28" t="n">
-        <v>79607</v>
+        <v>90905</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3446,25 +3441,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>2062</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3474,10 +3469,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577445</v>
+        <v>577523</v>
       </c>
       <c r="R28" t="n">
-        <v>7078496</v>
+        <v>7078418</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3536,10 +3531,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119873251</v>
+        <v>119871269</v>
       </c>
       <c r="B29" t="n">
-        <v>90527</v>
+        <v>78526</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3548,38 +3543,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577491</v>
+        <v>577631</v>
       </c>
       <c r="R29" t="n">
-        <v>7078459</v>
+        <v>7078350</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3626,22 +3621,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119872304</v>
+        <v>119873602</v>
       </c>
       <c r="B30" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3654,21 +3649,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3678,10 +3673,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577577</v>
+        <v>577440</v>
       </c>
       <c r="R30" t="n">
-        <v>7078356</v>
+        <v>7078487</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3708,12 +3703,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3740,7 +3735,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119872102</v>
+        <v>119872304</v>
       </c>
       <c r="B31" t="n">
         <v>90562</v>
@@ -3780,13 +3775,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577567</v>
+        <v>577577</v>
       </c>
       <c r="R31" t="n">
-        <v>7078377</v>
+        <v>7078356</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3810,12 +3805,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3842,10 +3837,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119871122</v>
+        <v>119873018</v>
       </c>
       <c r="B32" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3858,21 +3853,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3882,10 +3877,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577641</v>
+        <v>577513</v>
       </c>
       <c r="R32" t="n">
-        <v>7078334</v>
+        <v>7078427</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3944,10 +3939,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119873315</v>
+        <v>119871000</v>
       </c>
       <c r="B33" t="n">
-        <v>78526</v>
+        <v>90846</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3960,21 +3955,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3984,10 +3979,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577459</v>
+        <v>577653</v>
       </c>
       <c r="R33" t="n">
-        <v>7078453</v>
+        <v>7078341</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4046,10 +4041,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119871541</v>
+        <v>119871910</v>
       </c>
       <c r="B34" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4062,21 +4057,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4086,10 +4081,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577611</v>
+        <v>577581</v>
       </c>
       <c r="R34" t="n">
-        <v>7078365</v>
+        <v>7078410</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4148,10 +4143,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119874310</v>
+        <v>119873589</v>
       </c>
       <c r="B35" t="n">
-        <v>95202</v>
+        <v>57463</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4160,41 +4155,46 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2869</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577326</v>
+        <v>577449</v>
       </c>
       <c r="R35" t="n">
-        <v>7078610</v>
+        <v>7078490</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4238,22 +4238,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119871099</v>
+        <v>119871920</v>
       </c>
       <c r="B36" t="n">
-        <v>90846</v>
+        <v>90562</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4266,21 +4266,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4290,10 +4290,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577650</v>
+        <v>577561</v>
       </c>
       <c r="R36" t="n">
-        <v>7078332</v>
+        <v>7078431</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4320,12 +4320,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4352,10 +4352,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119873713</v>
+        <v>119874310</v>
       </c>
       <c r="B37" t="n">
-        <v>96862</v>
+        <v>95202</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4368,21 +4368,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>2869</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>577422</v>
+        <v>577326</v>
       </c>
       <c r="R37" t="n">
-        <v>7078461</v>
+        <v>7078610</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4442,22 +4442,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119871033</v>
+        <v>119873251</v>
       </c>
       <c r="B38" t="n">
-        <v>90846</v>
+        <v>90527</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4466,38 +4466,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577647</v>
+        <v>577491</v>
       </c>
       <c r="R38" t="n">
-        <v>7078328</v>
+        <v>7078459</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4544,22 +4544,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119871269</v>
+        <v>119872285</v>
       </c>
       <c r="B39" t="n">
-        <v>78526</v>
+        <v>90846</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4572,34 +4572,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577631</v>
+        <v>577564</v>
       </c>
       <c r="R39" t="n">
-        <v>7078350</v>
+        <v>7078366</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4646,22 +4646,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119873574</v>
+        <v>119871553</v>
       </c>
       <c r="B40" t="n">
-        <v>79643</v>
+        <v>79607</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4670,25 +4670,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4698,10 +4698,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577449</v>
+        <v>577606</v>
       </c>
       <c r="R40" t="n">
-        <v>7078503</v>
+        <v>7078395</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4748,22 +4748,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119873728</v>
+        <v>119871541</v>
       </c>
       <c r="B41" t="n">
-        <v>90580</v>
+        <v>90562</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4776,34 +4776,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577416</v>
+        <v>577611</v>
       </c>
       <c r="R41" t="n">
-        <v>7078478</v>
+        <v>7078365</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4862,10 +4862,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119872285</v>
+        <v>119873062</v>
       </c>
       <c r="B42" t="n">
-        <v>90846</v>
+        <v>97907</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4874,38 +4874,42 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577564</v>
+        <v>577511</v>
       </c>
       <c r="R42" t="n">
-        <v>7078366</v>
+        <v>7078434</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4964,10 +4968,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119873062</v>
+        <v>119873315</v>
       </c>
       <c r="B43" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4976,42 +4980,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577511</v>
+        <v>577459</v>
       </c>
       <c r="R43" t="n">
-        <v>7078434</v>
+        <v>7078453</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -2409,10 +2409,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119873866</v>
+        <v>119872671</v>
       </c>
       <c r="B18" t="n">
-        <v>78526</v>
+        <v>90846</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2425,34 +2425,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577389</v>
+        <v>577506</v>
       </c>
       <c r="R18" t="n">
-        <v>7078502</v>
+        <v>7078431</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2511,7 +2511,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119872671</v>
+        <v>119871099</v>
       </c>
       <c r="B19" t="n">
         <v>90846</v>
@@ -2547,14 +2547,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>577506</v>
+        <v>577650</v>
       </c>
       <c r="R19" t="n">
-        <v>7078431</v>
+        <v>7078332</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2601,22 +2601,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119871099</v>
+        <v>119873866</v>
       </c>
       <c r="B20" t="n">
-        <v>90846</v>
+        <v>78526</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2629,21 +2629,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577650</v>
+        <v>577389</v>
       </c>
       <c r="R20" t="n">
-        <v>7078332</v>
+        <v>7078502</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2703,12 +2703,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -4352,10 +4352,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119874310</v>
+        <v>119873251</v>
       </c>
       <c r="B37" t="n">
-        <v>95202</v>
+        <v>90527</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4368,34 +4368,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2869</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>577326</v>
+        <v>577491</v>
       </c>
       <c r="R37" t="n">
-        <v>7078610</v>
+        <v>7078459</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4454,10 +4454,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119873251</v>
+        <v>119871553</v>
       </c>
       <c r="B38" t="n">
-        <v>90527</v>
+        <v>79607</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4466,38 +4466,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577491</v>
+        <v>577606</v>
       </c>
       <c r="R38" t="n">
-        <v>7078459</v>
+        <v>7078395</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4524,12 +4524,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4544,22 +4544,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119872285</v>
+        <v>119874310</v>
       </c>
       <c r="B39" t="n">
-        <v>90846</v>
+        <v>95202</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4568,38 +4568,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>2869</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577564</v>
+        <v>577326</v>
       </c>
       <c r="R39" t="n">
-        <v>7078366</v>
+        <v>7078610</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4658,10 +4658,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119871553</v>
+        <v>119872285</v>
       </c>
       <c r="B40" t="n">
-        <v>79607</v>
+        <v>90846</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4674,34 +4674,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577606</v>
+        <v>577564</v>
       </c>
       <c r="R40" t="n">
-        <v>7078395</v>
+        <v>7078366</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4748,12 +4748,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -2001,7 +2001,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119872658</v>
+        <v>119872304</v>
       </c>
       <c r="B14" t="n">
         <v>90562</v>
@@ -2037,14 +2037,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577509</v>
+        <v>577577</v>
       </c>
       <c r="R14" t="n">
-        <v>7078448</v>
+        <v>7078356</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2071,12 +2071,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2091,22 +2091,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119873713</v>
+        <v>119871327</v>
       </c>
       <c r="B15" t="n">
-        <v>96862</v>
+        <v>90562</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2115,38 +2115,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577422</v>
+        <v>577636</v>
       </c>
       <c r="R15" t="n">
-        <v>7078461</v>
+        <v>7078360</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2193,22 +2193,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119873728</v>
+        <v>119871269</v>
       </c>
       <c r="B16" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577416</v>
+        <v>577631</v>
       </c>
       <c r="R16" t="n">
-        <v>7078478</v>
+        <v>7078350</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2295,22 +2295,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119871569</v>
+        <v>119873315</v>
       </c>
       <c r="B17" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2319,41 +2319,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577607</v>
+        <v>577459</v>
       </c>
       <c r="R17" t="n">
-        <v>7078381</v>
+        <v>7078453</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2377,12 +2377,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2397,19 +2397,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119872671</v>
+        <v>119871000</v>
       </c>
       <c r="B18" t="n">
         <v>90846</v>
@@ -2445,14 +2445,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577506</v>
+        <v>577653</v>
       </c>
       <c r="R18" t="n">
-        <v>7078431</v>
+        <v>7078341</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119871099</v>
+        <v>119872658</v>
       </c>
       <c r="B19" t="n">
-        <v>90846</v>
+        <v>90562</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2527,34 +2527,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>577650</v>
+        <v>577509</v>
       </c>
       <c r="R19" t="n">
-        <v>7078332</v>
+        <v>7078448</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2601,19 +2601,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119873866</v>
+        <v>119871910</v>
       </c>
       <c r="B20" t="n">
         <v>78526</v>
@@ -2649,14 +2649,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577389</v>
+        <v>577581</v>
       </c>
       <c r="R20" t="n">
-        <v>7078502</v>
+        <v>7078410</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2715,7 +2715,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119871033</v>
+        <v>119871099</v>
       </c>
       <c r="B21" t="n">
         <v>90846</v>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577647</v>
+        <v>577650</v>
       </c>
       <c r="R21" t="n">
-        <v>7078328</v>
+        <v>7078332</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119872102</v>
+        <v>119872661</v>
       </c>
       <c r="B22" t="n">
-        <v>90562</v>
+        <v>90905</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2829,25 +2829,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2857,13 +2857,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577567</v>
+        <v>577523</v>
       </c>
       <c r="R22" t="n">
-        <v>7078377</v>
+        <v>7078418</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119871327</v>
+        <v>119871122</v>
       </c>
       <c r="B23" t="n">
         <v>90562</v>
@@ -2955,14 +2955,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577636</v>
+        <v>577641</v>
       </c>
       <c r="R23" t="n">
-        <v>7078360</v>
+        <v>7078334</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3009,22 +3009,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119873511</v>
+        <v>119870839</v>
       </c>
       <c r="B24" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3037,34 +3037,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577445</v>
+        <v>577741</v>
       </c>
       <c r="R24" t="n">
-        <v>7078496</v>
+        <v>7078329</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3111,22 +3111,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119871122</v>
+        <v>119873602</v>
       </c>
       <c r="B25" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3139,21 +3139,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577641</v>
+        <v>577440</v>
       </c>
       <c r="R25" t="n">
-        <v>7078334</v>
+        <v>7078487</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3225,10 +3225,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119873574</v>
+        <v>119873713</v>
       </c>
       <c r="B26" t="n">
-        <v>79643</v>
+        <v>96862</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3241,21 +3241,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6464</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577449</v>
+        <v>577422</v>
       </c>
       <c r="R26" t="n">
-        <v>7078503</v>
+        <v>7078461</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3315,22 +3315,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119870839</v>
+        <v>119871541</v>
       </c>
       <c r="B27" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3343,21 +3343,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577741</v>
+        <v>577611</v>
       </c>
       <c r="R27" t="n">
-        <v>7078329</v>
+        <v>7078365</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3429,10 +3429,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119872661</v>
+        <v>119871920</v>
       </c>
       <c r="B28" t="n">
-        <v>90905</v>
+        <v>90562</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3441,25 +3441,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577523</v>
+        <v>577561</v>
       </c>
       <c r="R28" t="n">
-        <v>7078418</v>
+        <v>7078431</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3499,12 +3499,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3531,10 +3531,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119871269</v>
+        <v>119873728</v>
       </c>
       <c r="B29" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3547,21 +3547,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577631</v>
+        <v>577416</v>
       </c>
       <c r="R29" t="n">
-        <v>7078350</v>
+        <v>7078478</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3621,22 +3621,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119873602</v>
+        <v>119874310</v>
       </c>
       <c r="B30" t="n">
-        <v>78526</v>
+        <v>95202</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3645,25 +3645,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577440</v>
+        <v>577326</v>
       </c>
       <c r="R30" t="n">
-        <v>7078487</v>
+        <v>7078610</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3723,22 +3723,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119872304</v>
+        <v>119873589</v>
       </c>
       <c r="B31" t="n">
-        <v>90562</v>
+        <v>57463</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3751,37 +3751,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577577</v>
+        <v>577449</v>
       </c>
       <c r="R31" t="n">
-        <v>7078356</v>
+        <v>7078490</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3805,12 +3810,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3837,10 +3842,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119873018</v>
+        <v>119872102</v>
       </c>
       <c r="B32" t="n">
-        <v>90580</v>
+        <v>90562</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3853,21 +3858,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3877,13 +3882,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577513</v>
+        <v>577567</v>
       </c>
       <c r="R32" t="n">
-        <v>7078427</v>
+        <v>7078377</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3939,7 +3944,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119871000</v>
+        <v>119872671</v>
       </c>
       <c r="B33" t="n">
         <v>90846</v>
@@ -3975,14 +3980,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577653</v>
+        <v>577506</v>
       </c>
       <c r="R33" t="n">
-        <v>7078341</v>
+        <v>7078431</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4041,10 +4046,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119871910</v>
+        <v>119871569</v>
       </c>
       <c r="B34" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4053,41 +4058,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577581</v>
+        <v>577607</v>
       </c>
       <c r="R34" t="n">
-        <v>7078410</v>
+        <v>7078381</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4111,12 +4116,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4131,22 +4136,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119873589</v>
+        <v>119873062</v>
       </c>
       <c r="B35" t="n">
-        <v>57463</v>
+        <v>97907</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4155,46 +4160,45 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577449</v>
+        <v>577511</v>
       </c>
       <c r="R35" t="n">
-        <v>7078490</v>
+        <v>7078434</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4238,22 +4242,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119871920</v>
+        <v>119873511</v>
       </c>
       <c r="B36" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4266,21 +4270,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4290,10 +4294,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577561</v>
+        <v>577445</v>
       </c>
       <c r="R36" t="n">
-        <v>7078431</v>
+        <v>7078496</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4320,12 +4324,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4352,10 +4356,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119873251</v>
+        <v>119873866</v>
       </c>
       <c r="B37" t="n">
-        <v>90527</v>
+        <v>78526</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4364,38 +4368,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>577491</v>
+        <v>577389</v>
       </c>
       <c r="R37" t="n">
-        <v>7078459</v>
+        <v>7078502</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4454,10 +4458,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119871553</v>
+        <v>119873018</v>
       </c>
       <c r="B38" t="n">
-        <v>79607</v>
+        <v>90580</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4470,21 +4474,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4494,10 +4498,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577606</v>
+        <v>577513</v>
       </c>
       <c r="R38" t="n">
-        <v>7078395</v>
+        <v>7078427</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4524,12 +4528,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4556,10 +4560,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119874310</v>
+        <v>119873574</v>
       </c>
       <c r="B39" t="n">
-        <v>95202</v>
+        <v>79643</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4572,21 +4576,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2869</v>
+        <v>6464</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4596,10 +4600,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577326</v>
+        <v>577449</v>
       </c>
       <c r="R39" t="n">
-        <v>7078610</v>
+        <v>7078503</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4658,10 +4662,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119872285</v>
+        <v>119871553</v>
       </c>
       <c r="B40" t="n">
-        <v>90846</v>
+        <v>79607</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4674,34 +4678,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577564</v>
+        <v>577606</v>
       </c>
       <c r="R40" t="n">
-        <v>7078366</v>
+        <v>7078395</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4728,12 +4732,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4748,22 +4752,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119871541</v>
+        <v>119871033</v>
       </c>
       <c r="B41" t="n">
-        <v>90562</v>
+        <v>90846</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4776,34 +4780,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577611</v>
+        <v>577647</v>
       </c>
       <c r="R41" t="n">
-        <v>7078365</v>
+        <v>7078328</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4850,22 +4854,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119873062</v>
+        <v>119872285</v>
       </c>
       <c r="B42" t="n">
-        <v>97907</v>
+        <v>90846</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4874,42 +4878,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577511</v>
+        <v>577564</v>
       </c>
       <c r="R42" t="n">
-        <v>7078434</v>
+        <v>7078366</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4968,10 +4968,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119873315</v>
+        <v>119873251</v>
       </c>
       <c r="B43" t="n">
-        <v>78526</v>
+        <v>90527</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4980,25 +4980,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5008,10 +5008,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577459</v>
+        <v>577491</v>
       </c>
       <c r="R43" t="n">
-        <v>7078453</v>
+        <v>7078459</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -2715,10 +2715,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119871099</v>
+        <v>119872661</v>
       </c>
       <c r="B21" t="n">
-        <v>90846</v>
+        <v>90905</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2727,25 +2727,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>2062</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577650</v>
+        <v>577523</v>
       </c>
       <c r="R21" t="n">
-        <v>7078332</v>
+        <v>7078418</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119872661</v>
+        <v>119871099</v>
       </c>
       <c r="B22" t="n">
-        <v>90905</v>
+        <v>90846</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2829,25 +2829,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577523</v>
+        <v>577650</v>
       </c>
       <c r="R22" t="n">
-        <v>7078418</v>
+        <v>7078332</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -2001,10 +2001,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119872304</v>
+        <v>119871553</v>
       </c>
       <c r="B14" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577577</v>
+        <v>577606</v>
       </c>
       <c r="R14" t="n">
-        <v>7078356</v>
+        <v>7078395</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119871327</v>
+        <v>119871122</v>
       </c>
       <c r="B15" t="n">
         <v>90562</v>
@@ -2139,14 +2139,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577636</v>
+        <v>577641</v>
       </c>
       <c r="R15" t="n">
-        <v>7078360</v>
+        <v>7078334</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2193,22 +2193,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119871269</v>
+        <v>119871099</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
+        <v>90846</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577631</v>
+        <v>577650</v>
       </c>
       <c r="R16" t="n">
-        <v>7078350</v>
+        <v>7078332</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119873315</v>
+        <v>119873018</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2323,34 +2323,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577459</v>
+        <v>577513</v>
       </c>
       <c r="R17" t="n">
-        <v>7078453</v>
+        <v>7078427</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2397,22 +2397,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119871000</v>
+        <v>119873589</v>
       </c>
       <c r="B18" t="n">
-        <v>90846</v>
+        <v>57463</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2425,37 +2425,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577653</v>
+        <v>577449</v>
       </c>
       <c r="R18" t="n">
-        <v>7078341</v>
+        <v>7078490</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2499,22 +2504,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119872658</v>
+        <v>119873866</v>
       </c>
       <c r="B19" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2527,34 +2532,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>577509</v>
+        <v>577389</v>
       </c>
       <c r="R19" t="n">
-        <v>7078448</v>
+        <v>7078502</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2613,10 +2618,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119871910</v>
+        <v>119872102</v>
       </c>
       <c r="B20" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2629,37 +2634,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577581</v>
+        <v>577567</v>
       </c>
       <c r="R20" t="n">
-        <v>7078410</v>
+        <v>7078377</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2703,22 +2708,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119872661</v>
+        <v>119871000</v>
       </c>
       <c r="B21" t="n">
-        <v>90905</v>
+        <v>90846</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2727,38 +2732,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577523</v>
+        <v>577653</v>
       </c>
       <c r="R21" t="n">
-        <v>7078418</v>
+        <v>7078341</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2805,19 +2810,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119871099</v>
+        <v>119872285</v>
       </c>
       <c r="B22" t="n">
         <v>90846</v>
@@ -2853,14 +2858,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577650</v>
+        <v>577564</v>
       </c>
       <c r="R22" t="n">
-        <v>7078332</v>
+        <v>7078366</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2907,22 +2912,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119871122</v>
+        <v>119873315</v>
       </c>
       <c r="B23" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2935,34 +2940,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577641</v>
+        <v>577459</v>
       </c>
       <c r="R23" t="n">
-        <v>7078334</v>
+        <v>7078453</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3009,19 +3014,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119870839</v>
+        <v>119873602</v>
       </c>
       <c r="B24" t="n">
         <v>78526</v>
@@ -3057,14 +3062,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577741</v>
+        <v>577440</v>
       </c>
       <c r="R24" t="n">
-        <v>7078329</v>
+        <v>7078487</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3111,22 +3116,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119873602</v>
+        <v>119872661</v>
       </c>
       <c r="B25" t="n">
-        <v>78526</v>
+        <v>90905</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3135,25 +3140,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3163,10 +3168,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577440</v>
+        <v>577523</v>
       </c>
       <c r="R25" t="n">
-        <v>7078487</v>
+        <v>7078418</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3225,10 +3230,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119873713</v>
+        <v>119872658</v>
       </c>
       <c r="B26" t="n">
-        <v>96862</v>
+        <v>90562</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3237,38 +3242,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577422</v>
+        <v>577509</v>
       </c>
       <c r="R26" t="n">
-        <v>7078461</v>
+        <v>7078448</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3315,22 +3320,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119871541</v>
+        <v>119872671</v>
       </c>
       <c r="B27" t="n">
-        <v>90562</v>
+        <v>90846</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3343,34 +3348,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577611</v>
+        <v>577506</v>
       </c>
       <c r="R27" t="n">
-        <v>7078365</v>
+        <v>7078431</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3429,10 +3434,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119871920</v>
+        <v>119870839</v>
       </c>
       <c r="B28" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3445,34 +3450,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577561</v>
+        <v>577741</v>
       </c>
       <c r="R28" t="n">
-        <v>7078431</v>
+        <v>7078329</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3499,12 +3504,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3519,22 +3524,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119873728</v>
+        <v>119873574</v>
       </c>
       <c r="B29" t="n">
-        <v>90580</v>
+        <v>79643</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3543,25 +3548,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3571,10 +3576,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577416</v>
+        <v>577449</v>
       </c>
       <c r="R29" t="n">
-        <v>7078478</v>
+        <v>7078503</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3633,10 +3638,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119874310</v>
+        <v>119871910</v>
       </c>
       <c r="B30" t="n">
-        <v>95202</v>
+        <v>78526</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3645,38 +3650,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577326</v>
+        <v>577581</v>
       </c>
       <c r="R30" t="n">
-        <v>7078610</v>
+        <v>7078410</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3735,10 +3740,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119873589</v>
+        <v>119871269</v>
       </c>
       <c r="B31" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3751,42 +3756,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577449</v>
+        <v>577631</v>
       </c>
       <c r="R31" t="n">
-        <v>7078490</v>
+        <v>7078350</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3842,10 +3842,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119872102</v>
+        <v>119871033</v>
       </c>
       <c r="B32" t="n">
-        <v>90562</v>
+        <v>90846</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3858,21 +3858,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3882,13 +3882,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577567</v>
+        <v>577647</v>
       </c>
       <c r="R32" t="n">
-        <v>7078377</v>
+        <v>7078328</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3944,10 +3944,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119872671</v>
+        <v>119872304</v>
       </c>
       <c r="B33" t="n">
-        <v>90846</v>
+        <v>90562</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3960,34 +3960,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577506</v>
+        <v>577577</v>
       </c>
       <c r="R33" t="n">
-        <v>7078431</v>
+        <v>7078356</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4014,12 +4014,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4034,22 +4034,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119871569</v>
+        <v>119873511</v>
       </c>
       <c r="B34" t="n">
-        <v>79636</v>
+        <v>79607</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4058,25 +4058,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4086,13 +4086,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577607</v>
+        <v>577445</v>
       </c>
       <c r="R34" t="n">
-        <v>7078381</v>
+        <v>7078496</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4116,12 +4116,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4148,10 +4148,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119873062</v>
+        <v>119871541</v>
       </c>
       <c r="B35" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4160,42 +4160,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577511</v>
+        <v>577611</v>
       </c>
       <c r="R35" t="n">
-        <v>7078434</v>
+        <v>7078365</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4254,10 +4250,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119873511</v>
+        <v>119871920</v>
       </c>
       <c r="B36" t="n">
-        <v>79607</v>
+        <v>90562</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4270,21 +4266,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4294,10 +4290,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577445</v>
+        <v>577561</v>
       </c>
       <c r="R36" t="n">
-        <v>7078496</v>
+        <v>7078431</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4324,12 +4320,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4356,10 +4352,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119873866</v>
+        <v>119873713</v>
       </c>
       <c r="B37" t="n">
-        <v>78526</v>
+        <v>96862</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4368,25 +4364,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4396,10 +4392,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>577389</v>
+        <v>577422</v>
       </c>
       <c r="R37" t="n">
-        <v>7078502</v>
+        <v>7078461</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4446,22 +4442,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119873018</v>
+        <v>119873062</v>
       </c>
       <c r="B38" t="n">
-        <v>90580</v>
+        <v>97907</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4470,38 +4466,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577513</v>
+        <v>577511</v>
       </c>
       <c r="R38" t="n">
-        <v>7078427</v>
+        <v>7078434</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4548,22 +4548,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119873574</v>
+        <v>119871569</v>
       </c>
       <c r="B39" t="n">
-        <v>79643</v>
+        <v>79636</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4576,21 +4576,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4600,13 +4600,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577449</v>
+        <v>577607</v>
       </c>
       <c r="R39" t="n">
-        <v>7078503</v>
+        <v>7078381</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4630,12 +4630,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4650,22 +4650,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119871553</v>
+        <v>119873728</v>
       </c>
       <c r="B40" t="n">
-        <v>79607</v>
+        <v>90580</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4678,21 +4678,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4702,10 +4702,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577606</v>
+        <v>577416</v>
       </c>
       <c r="R40" t="n">
-        <v>7078395</v>
+        <v>7078478</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4732,12 +4732,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4752,22 +4752,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119871033</v>
+        <v>119874310</v>
       </c>
       <c r="B41" t="n">
-        <v>90846</v>
+        <v>95202</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4776,25 +4776,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>2869</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577647</v>
+        <v>577326</v>
       </c>
       <c r="R41" t="n">
-        <v>7078328</v>
+        <v>7078610</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4854,22 +4854,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119872285</v>
+        <v>119871327</v>
       </c>
       <c r="B42" t="n">
-        <v>90846</v>
+        <v>90562</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4882,21 +4882,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4906,10 +4906,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577564</v>
+        <v>577636</v>
       </c>
       <c r="R42" t="n">
-        <v>7078366</v>
+        <v>7078360</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -2516,10 +2516,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119873866</v>
+        <v>119872102</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2532,21 +2532,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2556,13 +2556,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>577389</v>
+        <v>577567</v>
       </c>
       <c r="R19" t="n">
-        <v>7078502</v>
+        <v>7078377</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2606,22 +2606,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119872102</v>
+        <v>119873866</v>
       </c>
       <c r="B20" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2634,21 +2634,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577567</v>
+        <v>577389</v>
       </c>
       <c r="R20" t="n">
-        <v>7078377</v>
+        <v>7078502</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2708,22 +2708,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119871000</v>
+        <v>119873315</v>
       </c>
       <c r="B21" t="n">
-        <v>90846</v>
+        <v>78526</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2736,21 +2736,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577653</v>
+        <v>577459</v>
       </c>
       <c r="R21" t="n">
-        <v>7078341</v>
+        <v>7078453</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2822,10 +2822,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119872285</v>
+        <v>119873602</v>
       </c>
       <c r="B22" t="n">
-        <v>90846</v>
+        <v>78526</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2838,34 +2838,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577564</v>
+        <v>577440</v>
       </c>
       <c r="R22" t="n">
-        <v>7078366</v>
+        <v>7078487</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2912,22 +2912,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119873315</v>
+        <v>119871000</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
+        <v>90846</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2940,21 +2940,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577459</v>
+        <v>577653</v>
       </c>
       <c r="R23" t="n">
-        <v>7078453</v>
+        <v>7078341</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119873602</v>
+        <v>119872285</v>
       </c>
       <c r="B24" t="n">
-        <v>78526</v>
+        <v>90846</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3042,34 +3042,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577440</v>
+        <v>577564</v>
       </c>
       <c r="R24" t="n">
-        <v>7078487</v>
+        <v>7078366</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3116,12 +3116,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3536,10 +3536,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119873574</v>
+        <v>119871910</v>
       </c>
       <c r="B29" t="n">
-        <v>79643</v>
+        <v>78526</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3548,38 +3548,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577449</v>
+        <v>577581</v>
       </c>
       <c r="R29" t="n">
-        <v>7078503</v>
+        <v>7078410</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3638,10 +3638,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119871910</v>
+        <v>119873574</v>
       </c>
       <c r="B30" t="n">
-        <v>78526</v>
+        <v>79643</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3650,38 +3650,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577581</v>
+        <v>577449</v>
       </c>
       <c r="R30" t="n">
-        <v>7078410</v>
+        <v>7078503</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -2001,10 +2001,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119871553</v>
+        <v>119871122</v>
       </c>
       <c r="B14" t="n">
-        <v>79607</v>
+        <v>90562</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577606</v>
+        <v>577641</v>
       </c>
       <c r="R14" t="n">
-        <v>7078395</v>
+        <v>7078334</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2071,12 +2071,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2103,10 +2103,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119871122</v>
+        <v>119871099</v>
       </c>
       <c r="B15" t="n">
-        <v>90562</v>
+        <v>90846</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577641</v>
+        <v>577650</v>
       </c>
       <c r="R15" t="n">
-        <v>7078334</v>
+        <v>7078332</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119871099</v>
+        <v>119871553</v>
       </c>
       <c r="B16" t="n">
-        <v>90846</v>
+        <v>79607</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577650</v>
+        <v>577606</v>
       </c>
       <c r="R16" t="n">
-        <v>7078332</v>
+        <v>7078395</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2275,12 +2275,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2516,10 +2516,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119872102</v>
+        <v>119873866</v>
       </c>
       <c r="B19" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2532,21 +2532,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2556,13 +2556,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>577567</v>
+        <v>577389</v>
       </c>
       <c r="R19" t="n">
-        <v>7078377</v>
+        <v>7078502</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2606,22 +2606,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119873866</v>
+        <v>119872102</v>
       </c>
       <c r="B20" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2634,21 +2634,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577389</v>
+        <v>577567</v>
       </c>
       <c r="R20" t="n">
-        <v>7078502</v>
+        <v>7078377</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2708,12 +2708,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119871000</v>
+        <v>119872661</v>
       </c>
       <c r="B23" t="n">
-        <v>90846</v>
+        <v>90905</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2936,38 +2936,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>2062</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577653</v>
+        <v>577523</v>
       </c>
       <c r="R23" t="n">
-        <v>7078341</v>
+        <v>7078418</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3014,19 +3014,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119872285</v>
+        <v>119871000</v>
       </c>
       <c r="B24" t="n">
         <v>90846</v>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577564</v>
+        <v>577653</v>
       </c>
       <c r="R24" t="n">
-        <v>7078366</v>
+        <v>7078341</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3128,10 +3128,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119872661</v>
+        <v>119872285</v>
       </c>
       <c r="B25" t="n">
-        <v>90905</v>
+        <v>90846</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3140,38 +3140,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577523</v>
+        <v>577564</v>
       </c>
       <c r="R25" t="n">
-        <v>7078418</v>
+        <v>7078366</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3218,12 +3218,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3536,10 +3536,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119871910</v>
+        <v>119873574</v>
       </c>
       <c r="B29" t="n">
-        <v>78526</v>
+        <v>79643</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3548,38 +3548,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577581</v>
+        <v>577449</v>
       </c>
       <c r="R29" t="n">
-        <v>7078410</v>
+        <v>7078503</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3638,10 +3638,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119873574</v>
+        <v>119871910</v>
       </c>
       <c r="B30" t="n">
-        <v>79643</v>
+        <v>78526</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3650,38 +3650,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577449</v>
+        <v>577581</v>
       </c>
       <c r="R30" t="n">
-        <v>7078503</v>
+        <v>7078410</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -2001,10 +2001,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119871122</v>
+        <v>119871553</v>
       </c>
       <c r="B14" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577641</v>
+        <v>577606</v>
       </c>
       <c r="R14" t="n">
-        <v>7078334</v>
+        <v>7078395</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2071,12 +2071,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2103,10 +2103,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119871099</v>
+        <v>119871122</v>
       </c>
       <c r="B15" t="n">
-        <v>90846</v>
+        <v>90562</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577650</v>
+        <v>577641</v>
       </c>
       <c r="R15" t="n">
-        <v>7078332</v>
+        <v>7078334</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119871553</v>
+        <v>119871099</v>
       </c>
       <c r="B16" t="n">
-        <v>79607</v>
+        <v>90846</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577606</v>
+        <v>577650</v>
       </c>
       <c r="R16" t="n">
-        <v>7078395</v>
+        <v>7078332</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2275,12 +2275,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2516,10 +2516,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119873866</v>
+        <v>119872102</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2532,21 +2532,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2556,13 +2556,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>577389</v>
+        <v>577567</v>
       </c>
       <c r="R19" t="n">
-        <v>7078502</v>
+        <v>7078377</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2606,22 +2606,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119872102</v>
+        <v>119873866</v>
       </c>
       <c r="B20" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2634,21 +2634,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577567</v>
+        <v>577389</v>
       </c>
       <c r="R20" t="n">
-        <v>7078377</v>
+        <v>7078502</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2708,12 +2708,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -2001,10 +2001,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119871553</v>
+        <v>119871122</v>
       </c>
       <c r="B14" t="n">
-        <v>79607</v>
+        <v>90562</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577606</v>
+        <v>577641</v>
       </c>
       <c r="R14" t="n">
-        <v>7078395</v>
+        <v>7078334</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2071,12 +2071,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2103,10 +2103,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119871122</v>
+        <v>119871099</v>
       </c>
       <c r="B15" t="n">
-        <v>90562</v>
+        <v>90846</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577641</v>
+        <v>577650</v>
       </c>
       <c r="R15" t="n">
-        <v>7078334</v>
+        <v>7078332</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119871099</v>
+        <v>119871553</v>
       </c>
       <c r="B16" t="n">
-        <v>90846</v>
+        <v>79607</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577650</v>
+        <v>577606</v>
       </c>
       <c r="R16" t="n">
-        <v>7078332</v>
+        <v>7078395</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2275,12 +2275,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2720,10 +2720,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119873315</v>
+        <v>119871000</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
+        <v>90846</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2736,21 +2736,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577459</v>
+        <v>577653</v>
       </c>
       <c r="R21" t="n">
-        <v>7078453</v>
+        <v>7078341</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2822,10 +2822,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119873602</v>
+        <v>119872285</v>
       </c>
       <c r="B22" t="n">
-        <v>78526</v>
+        <v>90846</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2838,34 +2838,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577440</v>
+        <v>577564</v>
       </c>
       <c r="R22" t="n">
-        <v>7078487</v>
+        <v>7078366</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2912,22 +2912,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119872661</v>
+        <v>119873315</v>
       </c>
       <c r="B23" t="n">
-        <v>90905</v>
+        <v>78526</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2936,38 +2936,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577523</v>
+        <v>577459</v>
       </c>
       <c r="R23" t="n">
-        <v>7078418</v>
+        <v>7078453</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3014,22 +3014,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119871000</v>
+        <v>119873602</v>
       </c>
       <c r="B24" t="n">
-        <v>90846</v>
+        <v>78526</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3042,34 +3042,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577653</v>
+        <v>577440</v>
       </c>
       <c r="R24" t="n">
-        <v>7078341</v>
+        <v>7078487</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3116,22 +3116,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119872285</v>
+        <v>119872661</v>
       </c>
       <c r="B25" t="n">
-        <v>90846</v>
+        <v>90905</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3140,38 +3140,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>2062</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577564</v>
+        <v>577523</v>
       </c>
       <c r="R25" t="n">
-        <v>7078366</v>
+        <v>7078418</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3218,12 +3218,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -2001,10 +2001,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119871122</v>
+        <v>119871553</v>
       </c>
       <c r="B14" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577641</v>
+        <v>577606</v>
       </c>
       <c r="R14" t="n">
-        <v>7078334</v>
+        <v>7078395</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2071,12 +2071,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2103,10 +2103,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119871099</v>
+        <v>119871122</v>
       </c>
       <c r="B15" t="n">
-        <v>90846</v>
+        <v>90562</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577650</v>
+        <v>577641</v>
       </c>
       <c r="R15" t="n">
-        <v>7078332</v>
+        <v>7078334</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119871553</v>
+        <v>119871099</v>
       </c>
       <c r="B16" t="n">
-        <v>79607</v>
+        <v>90846</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577606</v>
+        <v>577650</v>
       </c>
       <c r="R16" t="n">
-        <v>7078395</v>
+        <v>7078332</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2275,12 +2275,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2720,10 +2720,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119871000</v>
+        <v>119873315</v>
       </c>
       <c r="B21" t="n">
-        <v>90846</v>
+        <v>78526</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2736,21 +2736,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577653</v>
+        <v>577459</v>
       </c>
       <c r="R21" t="n">
-        <v>7078341</v>
+        <v>7078453</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2822,10 +2822,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119872285</v>
+        <v>119873602</v>
       </c>
       <c r="B22" t="n">
-        <v>90846</v>
+        <v>78526</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2838,34 +2838,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577564</v>
+        <v>577440</v>
       </c>
       <c r="R22" t="n">
-        <v>7078366</v>
+        <v>7078487</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2912,22 +2912,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119873315</v>
+        <v>119872661</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
+        <v>90905</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2936,38 +2936,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577459</v>
+        <v>577523</v>
       </c>
       <c r="R23" t="n">
-        <v>7078453</v>
+        <v>7078418</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3014,22 +3014,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119873602</v>
+        <v>119871000</v>
       </c>
       <c r="B24" t="n">
-        <v>78526</v>
+        <v>90846</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3042,34 +3042,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577440</v>
+        <v>577653</v>
       </c>
       <c r="R24" t="n">
-        <v>7078487</v>
+        <v>7078341</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3116,22 +3116,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119872661</v>
+        <v>119872285</v>
       </c>
       <c r="B25" t="n">
-        <v>90905</v>
+        <v>90846</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3140,38 +3140,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577523</v>
+        <v>577564</v>
       </c>
       <c r="R25" t="n">
-        <v>7078418</v>
+        <v>7078366</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3218,12 +3218,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -2516,10 +2516,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119872102</v>
+        <v>119873866</v>
       </c>
       <c r="B19" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2532,21 +2532,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2556,13 +2556,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>577567</v>
+        <v>577389</v>
       </c>
       <c r="R19" t="n">
-        <v>7078377</v>
+        <v>7078502</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2606,22 +2606,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119873866</v>
+        <v>119872102</v>
       </c>
       <c r="B20" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2634,21 +2634,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577389</v>
+        <v>577567</v>
       </c>
       <c r="R20" t="n">
-        <v>7078502</v>
+        <v>7078377</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2708,22 +2708,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119873315</v>
+        <v>119871000</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
+        <v>90846</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2736,21 +2736,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577459</v>
+        <v>577653</v>
       </c>
       <c r="R21" t="n">
-        <v>7078453</v>
+        <v>7078341</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2822,10 +2822,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119873602</v>
+        <v>119872285</v>
       </c>
       <c r="B22" t="n">
-        <v>78526</v>
+        <v>90846</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2838,34 +2838,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577440</v>
+        <v>577564</v>
       </c>
       <c r="R22" t="n">
-        <v>7078487</v>
+        <v>7078366</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2912,22 +2912,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119872661</v>
+        <v>119873315</v>
       </c>
       <c r="B23" t="n">
-        <v>90905</v>
+        <v>78526</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2936,38 +2936,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577523</v>
+        <v>577459</v>
       </c>
       <c r="R23" t="n">
-        <v>7078418</v>
+        <v>7078453</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3014,22 +3014,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119871000</v>
+        <v>119873602</v>
       </c>
       <c r="B24" t="n">
-        <v>90846</v>
+        <v>78526</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3042,34 +3042,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577653</v>
+        <v>577440</v>
       </c>
       <c r="R24" t="n">
-        <v>7078341</v>
+        <v>7078487</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3116,22 +3116,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119872285</v>
+        <v>119872661</v>
       </c>
       <c r="B25" t="n">
-        <v>90846</v>
+        <v>90905</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3140,38 +3140,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>2062</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577564</v>
+        <v>577523</v>
       </c>
       <c r="R25" t="n">
-        <v>7078366</v>
+        <v>7078418</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3218,12 +3218,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -2001,10 +2001,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119871553</v>
+        <v>119873866</v>
       </c>
       <c r="B14" t="n">
-        <v>79607</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577606</v>
+        <v>577389</v>
       </c>
       <c r="R14" t="n">
-        <v>7078395</v>
+        <v>7078502</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2071,12 +2071,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2091,22 +2091,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119871122</v>
+        <v>119873602</v>
       </c>
       <c r="B15" t="n">
-        <v>90562</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577641</v>
+        <v>577440</v>
       </c>
       <c r="R15" t="n">
-        <v>7078334</v>
+        <v>7078487</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119871099</v>
+        <v>119874310</v>
       </c>
       <c r="B16" t="n">
-        <v>90846</v>
+        <v>95225</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2217,25 +2217,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>2869</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577650</v>
+        <v>577326</v>
       </c>
       <c r="R16" t="n">
-        <v>7078332</v>
+        <v>7078610</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2295,22 +2295,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119873018</v>
+        <v>119871910</v>
       </c>
       <c r="B17" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2323,34 +2323,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577513</v>
+        <v>577581</v>
       </c>
       <c r="R17" t="n">
-        <v>7078427</v>
+        <v>7078410</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2397,22 +2397,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119873589</v>
+        <v>119873728</v>
       </c>
       <c r="B18" t="n">
-        <v>57463</v>
+        <v>90598</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2425,42 +2425,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577449</v>
+        <v>577416</v>
       </c>
       <c r="R18" t="n">
-        <v>7078490</v>
+        <v>7078478</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2504,22 +2499,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119873866</v>
+        <v>119870839</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2552,14 +2547,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>577389</v>
+        <v>577741</v>
       </c>
       <c r="R19" t="n">
-        <v>7078502</v>
+        <v>7078329</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2618,10 +2613,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119872102</v>
+        <v>119871920</v>
       </c>
       <c r="B20" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2658,13 +2653,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577567</v>
+        <v>577561</v>
       </c>
       <c r="R20" t="n">
-        <v>7078377</v>
+        <v>7078431</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2688,12 +2683,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2720,10 +2715,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119871000</v>
+        <v>119873589</v>
       </c>
       <c r="B21" t="n">
-        <v>90846</v>
+        <v>57473</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2736,37 +2731,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577653</v>
+        <v>577449</v>
       </c>
       <c r="R21" t="n">
-        <v>7078341</v>
+        <v>7078490</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2810,22 +2810,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119872285</v>
+        <v>119872658</v>
       </c>
       <c r="B22" t="n">
-        <v>90846</v>
+        <v>90580</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2838,34 +2838,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577564</v>
+        <v>577509</v>
       </c>
       <c r="R22" t="n">
-        <v>7078366</v>
+        <v>7078448</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119873315</v>
+        <v>119873018</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
+        <v>90598</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2940,34 +2940,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577459</v>
+        <v>577513</v>
       </c>
       <c r="R23" t="n">
-        <v>7078453</v>
+        <v>7078427</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3014,22 +3014,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119873602</v>
+        <v>119873713</v>
       </c>
       <c r="B24" t="n">
-        <v>78526</v>
+        <v>96885</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3038,25 +3038,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577440</v>
+        <v>577422</v>
       </c>
       <c r="R24" t="n">
-        <v>7078487</v>
+        <v>7078461</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3128,10 +3128,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119872661</v>
+        <v>119871541</v>
       </c>
       <c r="B25" t="n">
-        <v>90905</v>
+        <v>90580</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3140,38 +3140,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577523</v>
+        <v>577611</v>
       </c>
       <c r="R25" t="n">
-        <v>7078418</v>
+        <v>7078365</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3218,22 +3218,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119872658</v>
+        <v>119873511</v>
       </c>
       <c r="B26" t="n">
-        <v>90562</v>
+        <v>79623</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3246,34 +3246,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577509</v>
+        <v>577445</v>
       </c>
       <c r="R26" t="n">
-        <v>7078448</v>
+        <v>7078496</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3320,22 +3320,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119872671</v>
+        <v>119871122</v>
       </c>
       <c r="B27" t="n">
-        <v>90846</v>
+        <v>90580</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3348,34 +3348,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577506</v>
+        <v>577641</v>
       </c>
       <c r="R27" t="n">
-        <v>7078431</v>
+        <v>7078334</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3422,22 +3422,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119870839</v>
+        <v>119871553</v>
       </c>
       <c r="B28" t="n">
-        <v>78526</v>
+        <v>79623</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3450,34 +3450,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577741</v>
+        <v>577606</v>
       </c>
       <c r="R28" t="n">
-        <v>7078329</v>
+        <v>7078395</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3504,12 +3504,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3524,22 +3524,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119873574</v>
+        <v>119873062</v>
       </c>
       <c r="B29" t="n">
-        <v>79643</v>
+        <v>97930</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3548,38 +3548,42 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577449</v>
+        <v>577511</v>
       </c>
       <c r="R29" t="n">
-        <v>7078503</v>
+        <v>7078434</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3638,10 +3642,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119871910</v>
+        <v>119871569</v>
       </c>
       <c r="B30" t="n">
-        <v>78526</v>
+        <v>79652</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3650,41 +3654,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577581</v>
+        <v>577607</v>
       </c>
       <c r="R30" t="n">
-        <v>7078410</v>
+        <v>7078381</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3708,12 +3712,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3728,22 +3732,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119871269</v>
+        <v>119871033</v>
       </c>
       <c r="B31" t="n">
-        <v>78526</v>
+        <v>90864</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3756,21 +3760,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3780,10 +3784,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577631</v>
+        <v>577647</v>
       </c>
       <c r="R31" t="n">
-        <v>7078350</v>
+        <v>7078328</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3842,10 +3846,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119871033</v>
+        <v>119872285</v>
       </c>
       <c r="B32" t="n">
-        <v>90846</v>
+        <v>90864</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3878,14 +3882,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577647</v>
+        <v>577564</v>
       </c>
       <c r="R32" t="n">
-        <v>7078328</v>
+        <v>7078366</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3932,22 +3936,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119872304</v>
+        <v>119872102</v>
       </c>
       <c r="B33" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3984,13 +3988,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577577</v>
+        <v>577567</v>
       </c>
       <c r="R33" t="n">
-        <v>7078356</v>
+        <v>7078377</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4014,12 +4018,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4046,10 +4050,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119873511</v>
+        <v>119871000</v>
       </c>
       <c r="B34" t="n">
-        <v>79607</v>
+        <v>90864</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4062,34 +4066,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577445</v>
+        <v>577653</v>
       </c>
       <c r="R34" t="n">
-        <v>7078496</v>
+        <v>7078341</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4136,22 +4140,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119871541</v>
+        <v>119873251</v>
       </c>
       <c r="B35" t="n">
-        <v>90562</v>
+        <v>90545</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4160,25 +4164,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4188,10 +4192,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577611</v>
+        <v>577491</v>
       </c>
       <c r="R35" t="n">
-        <v>7078365</v>
+        <v>7078459</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4250,10 +4254,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119871920</v>
+        <v>119873574</v>
       </c>
       <c r="B36" t="n">
-        <v>90562</v>
+        <v>79659</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4262,25 +4266,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4290,10 +4294,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577561</v>
+        <v>577449</v>
       </c>
       <c r="R36" t="n">
-        <v>7078431</v>
+        <v>7078503</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4320,12 +4324,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4340,22 +4344,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119873713</v>
+        <v>119871327</v>
       </c>
       <c r="B37" t="n">
-        <v>96862</v>
+        <v>90580</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4364,38 +4368,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>577422</v>
+        <v>577636</v>
       </c>
       <c r="R37" t="n">
-        <v>7078461</v>
+        <v>7078360</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4442,22 +4446,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119873062</v>
+        <v>119872304</v>
       </c>
       <c r="B38" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4466,42 +4470,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577511</v>
+        <v>577577</v>
       </c>
       <c r="R38" t="n">
-        <v>7078434</v>
+        <v>7078356</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4528,12 +4528,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4548,22 +4548,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119871569</v>
+        <v>119871269</v>
       </c>
       <c r="B39" t="n">
-        <v>79636</v>
+        <v>78542</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4572,25 +4572,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4600,13 +4600,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577607</v>
+        <v>577631</v>
       </c>
       <c r="R39" t="n">
-        <v>7078381</v>
+        <v>7078350</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4630,12 +4630,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4662,10 +4662,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119873728</v>
+        <v>119871099</v>
       </c>
       <c r="B40" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4678,21 +4678,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4702,10 +4702,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577416</v>
+        <v>577650</v>
       </c>
       <c r="R40" t="n">
-        <v>7078478</v>
+        <v>7078332</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4752,22 +4752,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119874310</v>
+        <v>119872671</v>
       </c>
       <c r="B41" t="n">
-        <v>95202</v>
+        <v>90864</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4776,38 +4776,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2869</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577326</v>
+        <v>577506</v>
       </c>
       <c r="R41" t="n">
-        <v>7078610</v>
+        <v>7078431</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4866,10 +4866,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119871327</v>
+        <v>119873315</v>
       </c>
       <c r="B42" t="n">
-        <v>90562</v>
+        <v>78542</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4882,21 +4882,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4906,10 +4906,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577636</v>
+        <v>577459</v>
       </c>
       <c r="R42" t="n">
-        <v>7078360</v>
+        <v>7078453</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4968,10 +4968,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119873251</v>
+        <v>119872661</v>
       </c>
       <c r="B43" t="n">
-        <v>90527</v>
+        <v>90923</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4980,38 +4980,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>2062</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577491</v>
+        <v>577523</v>
       </c>
       <c r="R43" t="n">
-        <v>7078459</v>
+        <v>7078418</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5058,12 +5058,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5073,7 +5073,7 @@
         <v>119872241</v>
       </c>
       <c r="B44" t="n">
-        <v>91005</v>
+        <v>91023</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -2822,10 +2822,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119872658</v>
+        <v>119873713</v>
       </c>
       <c r="B22" t="n">
-        <v>90580</v>
+        <v>96885</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2834,38 +2834,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577509</v>
+        <v>577422</v>
       </c>
       <c r="R22" t="n">
-        <v>7078448</v>
+        <v>7078461</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2912,22 +2912,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119873018</v>
+        <v>119872658</v>
       </c>
       <c r="B23" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2940,34 +2940,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577513</v>
+        <v>577509</v>
       </c>
       <c r="R23" t="n">
-        <v>7078427</v>
+        <v>7078448</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3014,22 +3014,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119873713</v>
+        <v>119873018</v>
       </c>
       <c r="B24" t="n">
-        <v>96885</v>
+        <v>90598</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3038,25 +3038,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577422</v>
+        <v>577513</v>
       </c>
       <c r="R24" t="n">
-        <v>7078461</v>
+        <v>7078427</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3332,10 +3332,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119871122</v>
+        <v>119871553</v>
       </c>
       <c r="B27" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3348,21 +3348,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3372,10 +3372,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577641</v>
+        <v>577606</v>
       </c>
       <c r="R27" t="n">
-        <v>7078334</v>
+        <v>7078395</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3402,12 +3402,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3434,10 +3434,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119871553</v>
+        <v>119871122</v>
       </c>
       <c r="B28" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3450,21 +3450,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3474,10 +3474,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577606</v>
+        <v>577641</v>
       </c>
       <c r="R28" t="n">
-        <v>7078395</v>
+        <v>7078334</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3504,12 +3504,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3642,10 +3642,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119871569</v>
+        <v>119871033</v>
       </c>
       <c r="B30" t="n">
-        <v>79652</v>
+        <v>90864</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3654,25 +3654,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3682,13 +3682,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577607</v>
+        <v>577647</v>
       </c>
       <c r="R30" t="n">
-        <v>7078381</v>
+        <v>7078328</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3744,10 +3744,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119871033</v>
+        <v>119871569</v>
       </c>
       <c r="B31" t="n">
-        <v>90864</v>
+        <v>79652</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3756,25 +3756,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3784,13 +3784,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577647</v>
+        <v>577607</v>
       </c>
       <c r="R31" t="n">
-        <v>7078328</v>
+        <v>7078381</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4560,10 +4560,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119871269</v>
+        <v>119871099</v>
       </c>
       <c r="B39" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4576,21 +4576,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4600,10 +4600,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577631</v>
+        <v>577650</v>
       </c>
       <c r="R39" t="n">
-        <v>7078350</v>
+        <v>7078332</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4662,7 +4662,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119871099</v>
+        <v>119872671</v>
       </c>
       <c r="B40" t="n">
         <v>90864</v>
@@ -4698,14 +4698,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577650</v>
+        <v>577506</v>
       </c>
       <c r="R40" t="n">
-        <v>7078332</v>
+        <v>7078431</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4752,22 +4752,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119872671</v>
+        <v>119871269</v>
       </c>
       <c r="B41" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4780,34 +4780,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577506</v>
+        <v>577631</v>
       </c>
       <c r="R41" t="n">
-        <v>7078431</v>
+        <v>7078350</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4854,12 +4854,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -2001,7 +2001,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119873866</v>
+        <v>119871910</v>
       </c>
       <c r="B14" t="n">
         <v>78542</v>
@@ -2037,14 +2037,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577389</v>
+        <v>577581</v>
       </c>
       <c r="R14" t="n">
-        <v>7078502</v>
+        <v>7078410</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119873602</v>
+        <v>119873589</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2119,37 +2119,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577440</v>
+        <v>577449</v>
       </c>
       <c r="R15" t="n">
-        <v>7078487</v>
+        <v>7078490</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2205,10 +2210,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119874310</v>
+        <v>119872671</v>
       </c>
       <c r="B16" t="n">
-        <v>95225</v>
+        <v>90864</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2217,38 +2222,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2869</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577326</v>
+        <v>577506</v>
       </c>
       <c r="R16" t="n">
-        <v>7078610</v>
+        <v>7078431</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2307,10 +2312,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119871910</v>
+        <v>119871000</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2323,21 +2328,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2347,10 +2352,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577581</v>
+        <v>577653</v>
       </c>
       <c r="R17" t="n">
-        <v>7078410</v>
+        <v>7078341</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2409,10 +2414,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119873728</v>
+        <v>119871541</v>
       </c>
       <c r="B18" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2425,34 +2430,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577416</v>
+        <v>577611</v>
       </c>
       <c r="R18" t="n">
-        <v>7078478</v>
+        <v>7078365</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2511,10 +2516,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119870839</v>
+        <v>119872102</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2527,37 +2532,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>577741</v>
+        <v>577567</v>
       </c>
       <c r="R19" t="n">
-        <v>7078329</v>
+        <v>7078377</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2601,22 +2606,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119871920</v>
+        <v>119873018</v>
       </c>
       <c r="B20" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2629,21 +2634,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2653,10 +2658,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577561</v>
+        <v>577513</v>
       </c>
       <c r="R20" t="n">
-        <v>7078431</v>
+        <v>7078427</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2683,12 +2688,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2715,10 +2720,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119873589</v>
+        <v>119873713</v>
       </c>
       <c r="B21" t="n">
-        <v>57473</v>
+        <v>96885</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2727,46 +2732,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577449</v>
+        <v>577422</v>
       </c>
       <c r="R21" t="n">
-        <v>7078490</v>
+        <v>7078461</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2822,10 +2822,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119873713</v>
+        <v>119873728</v>
       </c>
       <c r="B22" t="n">
-        <v>96885</v>
+        <v>90598</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2834,25 +2834,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577422</v>
+        <v>577416</v>
       </c>
       <c r="R22" t="n">
-        <v>7078461</v>
+        <v>7078478</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2912,22 +2912,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119872658</v>
+        <v>119873062</v>
       </c>
       <c r="B23" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2936,38 +2936,42 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577509</v>
+        <v>577511</v>
       </c>
       <c r="R23" t="n">
-        <v>7078448</v>
+        <v>7078434</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3026,10 +3030,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119873018</v>
+        <v>119872304</v>
       </c>
       <c r="B24" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3042,21 +3046,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3066,10 +3070,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577513</v>
+        <v>577577</v>
       </c>
       <c r="R24" t="n">
-        <v>7078427</v>
+        <v>7078356</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3096,12 +3100,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3128,10 +3132,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119871541</v>
+        <v>119873602</v>
       </c>
       <c r="B25" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3144,34 +3148,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577611</v>
+        <v>577440</v>
       </c>
       <c r="R25" t="n">
-        <v>7078365</v>
+        <v>7078487</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3218,22 +3222,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119873511</v>
+        <v>119871269</v>
       </c>
       <c r="B26" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3246,21 +3250,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3270,10 +3274,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577445</v>
+        <v>577631</v>
       </c>
       <c r="R26" t="n">
-        <v>7078496</v>
+        <v>7078350</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3332,10 +3336,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119871553</v>
+        <v>119870839</v>
       </c>
       <c r="B27" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3348,34 +3352,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577606</v>
+        <v>577741</v>
       </c>
       <c r="R27" t="n">
-        <v>7078395</v>
+        <v>7078329</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3402,12 +3406,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3422,22 +3426,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119871122</v>
+        <v>119873315</v>
       </c>
       <c r="B28" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3450,34 +3454,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577641</v>
+        <v>577459</v>
       </c>
       <c r="R28" t="n">
-        <v>7078334</v>
+        <v>7078453</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3524,22 +3528,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119873062</v>
+        <v>119872658</v>
       </c>
       <c r="B29" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3548,42 +3552,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577511</v>
+        <v>577509</v>
       </c>
       <c r="R29" t="n">
-        <v>7078434</v>
+        <v>7078448</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3642,10 +3642,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119871033</v>
+        <v>119871920</v>
       </c>
       <c r="B30" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3658,21 +3658,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3682,10 +3682,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577647</v>
+        <v>577561</v>
       </c>
       <c r="R30" t="n">
-        <v>7078328</v>
+        <v>7078431</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3744,10 +3744,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119871569</v>
+        <v>119871327</v>
       </c>
       <c r="B31" t="n">
-        <v>79652</v>
+        <v>90580</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3756,41 +3756,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577607</v>
+        <v>577636</v>
       </c>
       <c r="R31" t="n">
-        <v>7078381</v>
+        <v>7078360</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3834,22 +3834,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119872285</v>
+        <v>119873251</v>
       </c>
       <c r="B32" t="n">
-        <v>90864</v>
+        <v>90545</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3858,25 +3858,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577564</v>
+        <v>577491</v>
       </c>
       <c r="R32" t="n">
-        <v>7078366</v>
+        <v>7078459</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3948,10 +3948,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119872102</v>
+        <v>119873574</v>
       </c>
       <c r="B33" t="n">
-        <v>90580</v>
+        <v>79659</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3960,25 +3960,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3988,13 +3988,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577567</v>
+        <v>577449</v>
       </c>
       <c r="R33" t="n">
-        <v>7078377</v>
+        <v>7078503</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4038,22 +4038,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119871000</v>
+        <v>119871122</v>
       </c>
       <c r="B34" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4066,34 +4066,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577653</v>
+        <v>577641</v>
       </c>
       <c r="R34" t="n">
-        <v>7078341</v>
+        <v>7078334</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4140,22 +4140,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119873251</v>
+        <v>119873511</v>
       </c>
       <c r="B35" t="n">
-        <v>90545</v>
+        <v>79623</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4164,38 +4164,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577491</v>
+        <v>577445</v>
       </c>
       <c r="R35" t="n">
-        <v>7078459</v>
+        <v>7078496</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4242,22 +4242,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119873574</v>
+        <v>119871569</v>
       </c>
       <c r="B36" t="n">
-        <v>79659</v>
+        <v>79652</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4270,21 +4270,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4294,13 +4294,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577449</v>
+        <v>577607</v>
       </c>
       <c r="R36" t="n">
-        <v>7078503</v>
+        <v>7078381</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4324,12 +4324,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4344,22 +4344,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119871327</v>
+        <v>119874310</v>
       </c>
       <c r="B37" t="n">
-        <v>90580</v>
+        <v>95225</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4368,38 +4368,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>577636</v>
+        <v>577326</v>
       </c>
       <c r="R37" t="n">
-        <v>7078360</v>
+        <v>7078610</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4458,10 +4458,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119872304</v>
+        <v>119872661</v>
       </c>
       <c r="B38" t="n">
-        <v>90580</v>
+        <v>90923</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4470,25 +4470,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577577</v>
+        <v>577523</v>
       </c>
       <c r="R38" t="n">
-        <v>7078356</v>
+        <v>7078418</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4528,12 +4528,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4560,10 +4560,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119871099</v>
+        <v>119871553</v>
       </c>
       <c r="B39" t="n">
-        <v>90864</v>
+        <v>79623</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4576,21 +4576,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4600,10 +4600,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577650</v>
+        <v>577606</v>
       </c>
       <c r="R39" t="n">
-        <v>7078332</v>
+        <v>7078395</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4630,12 +4630,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4662,10 +4662,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119872671</v>
+        <v>119873866</v>
       </c>
       <c r="B40" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4678,34 +4678,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577506</v>
+        <v>577389</v>
       </c>
       <c r="R40" t="n">
-        <v>7078431</v>
+        <v>7078502</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4764,10 +4764,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119871269</v>
+        <v>119872285</v>
       </c>
       <c r="B41" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4780,34 +4780,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577631</v>
+        <v>577564</v>
       </c>
       <c r="R41" t="n">
-        <v>7078350</v>
+        <v>7078366</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4854,22 +4854,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119873315</v>
+        <v>119871099</v>
       </c>
       <c r="B42" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4882,34 +4882,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577459</v>
+        <v>577650</v>
       </c>
       <c r="R42" t="n">
-        <v>7078453</v>
+        <v>7078332</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4956,22 +4956,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119872661</v>
+        <v>119871033</v>
       </c>
       <c r="B43" t="n">
-        <v>90923</v>
+        <v>90864</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4980,25 +4980,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5008,10 +5008,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577523</v>
+        <v>577647</v>
       </c>
       <c r="R43" t="n">
-        <v>7078418</v>
+        <v>7078328</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -4662,10 +4662,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119873866</v>
+        <v>119872285</v>
       </c>
       <c r="B40" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4678,34 +4678,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577389</v>
+        <v>577564</v>
       </c>
       <c r="R40" t="n">
-        <v>7078502</v>
+        <v>7078366</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4764,10 +4764,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119872285</v>
+        <v>119873866</v>
       </c>
       <c r="B41" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4780,34 +4780,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577564</v>
+        <v>577389</v>
       </c>
       <c r="R41" t="n">
-        <v>7078366</v>
+        <v>7078502</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -2001,10 +2001,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119871910</v>
+        <v>119874310</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>95225</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2013,38 +2013,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577581</v>
+        <v>577326</v>
       </c>
       <c r="R14" t="n">
-        <v>7078410</v>
+        <v>7078610</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119873589</v>
+        <v>119872658</v>
       </c>
       <c r="B15" t="n">
-        <v>57473</v>
+        <v>90580</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2119,42 +2119,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577449</v>
+        <v>577509</v>
       </c>
       <c r="R15" t="n">
-        <v>7078490</v>
+        <v>7078448</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2198,22 +2193,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119872671</v>
+        <v>119871122</v>
       </c>
       <c r="B16" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2226,34 +2221,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577506</v>
+        <v>577641</v>
       </c>
       <c r="R16" t="n">
-        <v>7078431</v>
+        <v>7078334</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2300,19 +2295,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119871000</v>
+        <v>119871099</v>
       </c>
       <c r="B17" t="n">
         <v>90864</v>
@@ -2348,14 +2343,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577653</v>
+        <v>577650</v>
       </c>
       <c r="R17" t="n">
-        <v>7078341</v>
+        <v>7078332</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2402,22 +2397,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119871541</v>
+        <v>119873511</v>
       </c>
       <c r="B18" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2430,34 +2425,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577611</v>
+        <v>577445</v>
       </c>
       <c r="R18" t="n">
-        <v>7078365</v>
+        <v>7078496</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2504,22 +2499,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119872102</v>
+        <v>119873602</v>
       </c>
       <c r="B19" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2532,21 +2527,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2556,13 +2551,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>577567</v>
+        <v>577440</v>
       </c>
       <c r="R19" t="n">
-        <v>7078377</v>
+        <v>7078487</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2618,10 +2613,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119873018</v>
+        <v>119871553</v>
       </c>
       <c r="B20" t="n">
-        <v>90598</v>
+        <v>79623</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2634,21 +2629,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2658,10 +2653,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577513</v>
+        <v>577606</v>
       </c>
       <c r="R20" t="n">
-        <v>7078427</v>
+        <v>7078395</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2688,12 +2683,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2720,10 +2715,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119873713</v>
+        <v>119873589</v>
       </c>
       <c r="B21" t="n">
-        <v>96885</v>
+        <v>57473</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2732,41 +2727,46 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577422</v>
+        <v>577449</v>
       </c>
       <c r="R21" t="n">
-        <v>7078461</v>
+        <v>7078490</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2822,10 +2822,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119873728</v>
+        <v>119873251</v>
       </c>
       <c r="B22" t="n">
-        <v>90598</v>
+        <v>90545</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2834,38 +2834,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577416</v>
+        <v>577491</v>
       </c>
       <c r="R22" t="n">
-        <v>7078478</v>
+        <v>7078459</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3030,10 +3030,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119872304</v>
+        <v>119872285</v>
       </c>
       <c r="B24" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3046,34 +3046,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577577</v>
+        <v>577564</v>
       </c>
       <c r="R24" t="n">
-        <v>7078356</v>
+        <v>7078366</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3100,12 +3100,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3120,22 +3120,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119873602</v>
+        <v>119873018</v>
       </c>
       <c r="B25" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3148,21 +3148,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3172,10 +3172,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577440</v>
+        <v>577513</v>
       </c>
       <c r="R25" t="n">
-        <v>7078487</v>
+        <v>7078427</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3234,7 +3234,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119871269</v>
+        <v>119871910</v>
       </c>
       <c r="B26" t="n">
         <v>78542</v>
@@ -3270,14 +3270,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577631</v>
+        <v>577581</v>
       </c>
       <c r="R26" t="n">
-        <v>7078350</v>
+        <v>7078410</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3324,22 +3324,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119870839</v>
+        <v>119871033</v>
       </c>
       <c r="B27" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3352,34 +3352,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577741</v>
+        <v>577647</v>
       </c>
       <c r="R27" t="n">
-        <v>7078329</v>
+        <v>7078328</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3426,22 +3426,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119873315</v>
+        <v>119871000</v>
       </c>
       <c r="B28" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3454,21 +3454,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3478,10 +3478,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577459</v>
+        <v>577653</v>
       </c>
       <c r="R28" t="n">
-        <v>7078453</v>
+        <v>7078341</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3540,7 +3540,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119872658</v>
+        <v>119871920</v>
       </c>
       <c r="B29" t="n">
         <v>90580</v>
@@ -3576,14 +3576,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577509</v>
+        <v>577561</v>
       </c>
       <c r="R29" t="n">
-        <v>7078448</v>
+        <v>7078431</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3630,22 +3630,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119871920</v>
+        <v>119872671</v>
       </c>
       <c r="B30" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3658,31 +3658,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577561</v>
+        <v>577506</v>
       </c>
       <c r="R30" t="n">
         <v>7078431</v>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3732,19 +3732,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119871327</v>
+        <v>119871541</v>
       </c>
       <c r="B31" t="n">
         <v>90580</v>
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577636</v>
+        <v>577611</v>
       </c>
       <c r="R31" t="n">
-        <v>7078360</v>
+        <v>7078365</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3846,10 +3846,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119873251</v>
+        <v>119873315</v>
       </c>
       <c r="B32" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3858,25 +3858,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577491</v>
+        <v>577459</v>
       </c>
       <c r="R32" t="n">
-        <v>7078459</v>
+        <v>7078453</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3948,10 +3948,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119873574</v>
+        <v>119872661</v>
       </c>
       <c r="B33" t="n">
-        <v>79659</v>
+        <v>90923</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3960,25 +3960,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6464</v>
+        <v>2062</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3988,10 +3988,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577449</v>
+        <v>577523</v>
       </c>
       <c r="R33" t="n">
-        <v>7078503</v>
+        <v>7078418</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4038,22 +4038,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119871122</v>
+        <v>119873728</v>
       </c>
       <c r="B34" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4066,21 +4066,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577641</v>
+        <v>577416</v>
       </c>
       <c r="R34" t="n">
-        <v>7078334</v>
+        <v>7078478</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4140,22 +4140,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119873511</v>
+        <v>119870839</v>
       </c>
       <c r="B35" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4168,34 +4168,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577445</v>
+        <v>577741</v>
       </c>
       <c r="R35" t="n">
-        <v>7078496</v>
+        <v>7078329</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4242,22 +4242,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119871569</v>
+        <v>119872304</v>
       </c>
       <c r="B36" t="n">
-        <v>79652</v>
+        <v>90580</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4266,25 +4266,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4294,13 +4294,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577607</v>
+        <v>577577</v>
       </c>
       <c r="R36" t="n">
-        <v>7078381</v>
+        <v>7078356</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4356,10 +4356,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119874310</v>
+        <v>119871569</v>
       </c>
       <c r="B37" t="n">
-        <v>95225</v>
+        <v>79652</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4372,21 +4372,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2869</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4396,13 +4396,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>577326</v>
+        <v>577607</v>
       </c>
       <c r="R37" t="n">
-        <v>7078610</v>
+        <v>7078381</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4426,12 +4426,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4446,22 +4446,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119872661</v>
+        <v>119871327</v>
       </c>
       <c r="B38" t="n">
-        <v>90923</v>
+        <v>90580</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4470,38 +4470,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577523</v>
+        <v>577636</v>
       </c>
       <c r="R38" t="n">
-        <v>7078418</v>
+        <v>7078360</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4548,22 +4548,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119871553</v>
+        <v>119873713</v>
       </c>
       <c r="B39" t="n">
-        <v>79623</v>
+        <v>96885</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4572,25 +4572,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4600,10 +4600,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577606</v>
+        <v>577422</v>
       </c>
       <c r="R39" t="n">
-        <v>7078395</v>
+        <v>7078461</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4630,12 +4630,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4662,10 +4662,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119872285</v>
+        <v>119871269</v>
       </c>
       <c r="B40" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4678,34 +4678,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577564</v>
+        <v>577631</v>
       </c>
       <c r="R40" t="n">
-        <v>7078366</v>
+        <v>7078350</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4752,22 +4752,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119873866</v>
+        <v>119873574</v>
       </c>
       <c r="B41" t="n">
-        <v>78542</v>
+        <v>79659</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4776,25 +4776,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577389</v>
+        <v>577449</v>
       </c>
       <c r="R41" t="n">
-        <v>7078502</v>
+        <v>7078503</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4866,10 +4866,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119871099</v>
+        <v>119872102</v>
       </c>
       <c r="B42" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4882,21 +4882,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4906,13 +4906,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577650</v>
+        <v>577567</v>
       </c>
       <c r="R42" t="n">
-        <v>7078332</v>
+        <v>7078377</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4968,10 +4968,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119871033</v>
+        <v>119873866</v>
       </c>
       <c r="B43" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4984,21 +4984,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5008,10 +5008,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577647</v>
+        <v>577389</v>
       </c>
       <c r="R43" t="n">
-        <v>7078328</v>
+        <v>7078502</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5058,12 +5058,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -2001,10 +2001,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119874310</v>
+        <v>119871033</v>
       </c>
       <c r="B14" t="n">
-        <v>95225</v>
+        <v>90864</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2013,25 +2013,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2869</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577326</v>
+        <v>577647</v>
       </c>
       <c r="R14" t="n">
-        <v>7078610</v>
+        <v>7078328</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2091,22 +2091,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119872658</v>
+        <v>119873574</v>
       </c>
       <c r="B15" t="n">
-        <v>90580</v>
+        <v>79659</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2115,38 +2115,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577509</v>
+        <v>577449</v>
       </c>
       <c r="R15" t="n">
-        <v>7078448</v>
+        <v>7078503</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119871122</v>
+        <v>119871269</v>
       </c>
       <c r="B16" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577641</v>
+        <v>577631</v>
       </c>
       <c r="R16" t="n">
-        <v>7078334</v>
+        <v>7078350</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2307,7 +2307,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119871099</v>
+        <v>119872671</v>
       </c>
       <c r="B17" t="n">
         <v>90864</v>
@@ -2343,14 +2343,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577650</v>
+        <v>577506</v>
       </c>
       <c r="R17" t="n">
-        <v>7078332</v>
+        <v>7078431</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2397,22 +2397,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119873511</v>
+        <v>119872285</v>
       </c>
       <c r="B18" t="n">
-        <v>79623</v>
+        <v>90864</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2425,34 +2425,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577445</v>
+        <v>577564</v>
       </c>
       <c r="R18" t="n">
-        <v>7078496</v>
+        <v>7078366</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2499,22 +2499,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119873602</v>
+        <v>119873589</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2527,37 +2527,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>577440</v>
+        <v>577449</v>
       </c>
       <c r="R19" t="n">
-        <v>7078487</v>
+        <v>7078490</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2613,10 +2618,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119871553</v>
+        <v>119873713</v>
       </c>
       <c r="B20" t="n">
-        <v>79623</v>
+        <v>96885</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2625,25 +2630,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2653,10 +2658,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577606</v>
+        <v>577422</v>
       </c>
       <c r="R20" t="n">
-        <v>7078395</v>
+        <v>7078461</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2683,12 +2688,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2715,10 +2720,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119873589</v>
+        <v>119874310</v>
       </c>
       <c r="B21" t="n">
-        <v>57473</v>
+        <v>95225</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2727,46 +2732,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>2869</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577449</v>
+        <v>577326</v>
       </c>
       <c r="R21" t="n">
-        <v>7078490</v>
+        <v>7078610</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2810,22 +2810,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119873251</v>
+        <v>119872658</v>
       </c>
       <c r="B22" t="n">
-        <v>90545</v>
+        <v>90580</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2834,38 +2834,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577491</v>
+        <v>577509</v>
       </c>
       <c r="R22" t="n">
-        <v>7078459</v>
+        <v>7078448</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119873062</v>
+        <v>119872304</v>
       </c>
       <c r="B23" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2936,42 +2936,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577511</v>
+        <v>577577</v>
       </c>
       <c r="R23" t="n">
-        <v>7078434</v>
+        <v>7078356</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2998,12 +2994,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3018,22 +3014,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119872285</v>
+        <v>119873315</v>
       </c>
       <c r="B24" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3046,21 +3042,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3070,10 +3066,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577564</v>
+        <v>577459</v>
       </c>
       <c r="R24" t="n">
-        <v>7078366</v>
+        <v>7078453</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3132,10 +3128,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119873018</v>
+        <v>119873866</v>
       </c>
       <c r="B25" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3148,21 +3144,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3172,10 +3168,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577513</v>
+        <v>577389</v>
       </c>
       <c r="R25" t="n">
-        <v>7078427</v>
+        <v>7078502</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3222,19 +3218,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119871910</v>
+        <v>119873602</v>
       </c>
       <c r="B26" t="n">
         <v>78542</v>
@@ -3270,14 +3266,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577581</v>
+        <v>577440</v>
       </c>
       <c r="R26" t="n">
-        <v>7078410</v>
+        <v>7078487</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3324,22 +3320,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119871033</v>
+        <v>119872102</v>
       </c>
       <c r="B27" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3352,21 +3348,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3376,13 +3372,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577647</v>
+        <v>577567</v>
       </c>
       <c r="R27" t="n">
-        <v>7078328</v>
+        <v>7078377</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3438,10 +3434,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119871000</v>
+        <v>119871553</v>
       </c>
       <c r="B28" t="n">
-        <v>90864</v>
+        <v>79623</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3454,34 +3450,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577653</v>
+        <v>577606</v>
       </c>
       <c r="R28" t="n">
-        <v>7078341</v>
+        <v>7078395</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3508,12 +3504,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3528,19 +3524,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119871920</v>
+        <v>119871327</v>
       </c>
       <c r="B29" t="n">
         <v>90580</v>
@@ -3576,14 +3572,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577561</v>
+        <v>577636</v>
       </c>
       <c r="R29" t="n">
-        <v>7078431</v>
+        <v>7078360</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3610,12 +3606,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3630,22 +3626,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119872671</v>
+        <v>119873251</v>
       </c>
       <c r="B30" t="n">
-        <v>90864</v>
+        <v>90545</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3654,38 +3650,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577506</v>
+        <v>577491</v>
       </c>
       <c r="R30" t="n">
-        <v>7078431</v>
+        <v>7078459</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3846,10 +3842,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119873315</v>
+        <v>119873062</v>
       </c>
       <c r="B32" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3858,38 +3854,42 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577459</v>
+        <v>577511</v>
       </c>
       <c r="R32" t="n">
-        <v>7078453</v>
+        <v>7078434</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3948,10 +3948,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119872661</v>
+        <v>119871000</v>
       </c>
       <c r="B33" t="n">
-        <v>90923</v>
+        <v>90864</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3960,38 +3960,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577523</v>
+        <v>577653</v>
       </c>
       <c r="R33" t="n">
-        <v>7078418</v>
+        <v>7078341</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4038,22 +4038,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119873728</v>
+        <v>119871910</v>
       </c>
       <c r="B34" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4066,34 +4066,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577416</v>
+        <v>577581</v>
       </c>
       <c r="R34" t="n">
-        <v>7078478</v>
+        <v>7078410</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4152,10 +4152,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119870839</v>
+        <v>119873511</v>
       </c>
       <c r="B35" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4168,34 +4168,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577741</v>
+        <v>577445</v>
       </c>
       <c r="R35" t="n">
-        <v>7078329</v>
+        <v>7078496</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4242,22 +4242,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119872304</v>
+        <v>119872661</v>
       </c>
       <c r="B36" t="n">
-        <v>90580</v>
+        <v>90923</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4266,25 +4266,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4294,10 +4294,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577577</v>
+        <v>577523</v>
       </c>
       <c r="R36" t="n">
-        <v>7078356</v>
+        <v>7078418</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4324,12 +4324,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4356,10 +4356,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119871569</v>
+        <v>119871099</v>
       </c>
       <c r="B37" t="n">
-        <v>79652</v>
+        <v>90864</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4368,25 +4368,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4396,13 +4396,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>577607</v>
+        <v>577650</v>
       </c>
       <c r="R37" t="n">
-        <v>7078381</v>
+        <v>7078332</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4426,12 +4426,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4458,10 +4458,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119871327</v>
+        <v>119873018</v>
       </c>
       <c r="B38" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4474,34 +4474,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577636</v>
+        <v>577513</v>
       </c>
       <c r="R38" t="n">
-        <v>7078360</v>
+        <v>7078427</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4548,22 +4548,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119873713</v>
+        <v>119871920</v>
       </c>
       <c r="B39" t="n">
-        <v>96885</v>
+        <v>90580</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4572,25 +4572,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4600,10 +4600,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577422</v>
+        <v>577561</v>
       </c>
       <c r="R39" t="n">
-        <v>7078461</v>
+        <v>7078431</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4630,12 +4630,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4662,7 +4662,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119871269</v>
+        <v>119870839</v>
       </c>
       <c r="B40" t="n">
         <v>78542</v>
@@ -4698,14 +4698,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577631</v>
+        <v>577741</v>
       </c>
       <c r="R40" t="n">
-        <v>7078350</v>
+        <v>7078329</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4752,22 +4752,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119873574</v>
+        <v>119873728</v>
       </c>
       <c r="B41" t="n">
-        <v>79659</v>
+        <v>90598</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4776,25 +4776,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577449</v>
+        <v>577416</v>
       </c>
       <c r="R41" t="n">
-        <v>7078503</v>
+        <v>7078478</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4866,7 +4866,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119872102</v>
+        <v>119871122</v>
       </c>
       <c r="B42" t="n">
         <v>90580</v>
@@ -4906,13 +4906,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577567</v>
+        <v>577641</v>
       </c>
       <c r="R42" t="n">
-        <v>7078377</v>
+        <v>7078334</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4968,10 +4968,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119873866</v>
+        <v>119871569</v>
       </c>
       <c r="B43" t="n">
-        <v>78542</v>
+        <v>79652</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4980,25 +4980,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5008,13 +5008,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577389</v>
+        <v>577607</v>
       </c>
       <c r="R43" t="n">
-        <v>7078502</v>
+        <v>7078381</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5038,12 +5038,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5058,12 +5058,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -2001,10 +2001,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119871033</v>
+        <v>119873018</v>
       </c>
       <c r="B14" t="n">
-        <v>90864</v>
+        <v>90598</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577647</v>
+        <v>577513</v>
       </c>
       <c r="R14" t="n">
-        <v>7078328</v>
+        <v>7078427</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119873574</v>
+        <v>119871000</v>
       </c>
       <c r="B15" t="n">
-        <v>79659</v>
+        <v>90864</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2115,38 +2115,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577449</v>
+        <v>577653</v>
       </c>
       <c r="R15" t="n">
-        <v>7078503</v>
+        <v>7078341</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119871269</v>
+        <v>119873511</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577631</v>
+        <v>577445</v>
       </c>
       <c r="R16" t="n">
-        <v>7078350</v>
+        <v>7078496</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2307,7 +2307,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119872671</v>
+        <v>119871033</v>
       </c>
       <c r="B17" t="n">
         <v>90864</v>
@@ -2343,14 +2343,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577506</v>
+        <v>577647</v>
       </c>
       <c r="R17" t="n">
-        <v>7078431</v>
+        <v>7078328</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2397,22 +2397,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119872285</v>
+        <v>119872102</v>
       </c>
       <c r="B18" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2425,37 +2425,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577564</v>
+        <v>577567</v>
       </c>
       <c r="R18" t="n">
-        <v>7078366</v>
+        <v>7078377</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2499,22 +2499,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119873589</v>
+        <v>119874310</v>
       </c>
       <c r="B19" t="n">
-        <v>57473</v>
+        <v>95225</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2523,46 +2523,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>2869</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>577449</v>
+        <v>577326</v>
       </c>
       <c r="R19" t="n">
-        <v>7078490</v>
+        <v>7078610</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2606,22 +2601,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119873713</v>
+        <v>119873728</v>
       </c>
       <c r="B20" t="n">
-        <v>96885</v>
+        <v>90598</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2630,25 +2625,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2658,10 +2653,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577422</v>
+        <v>577416</v>
       </c>
       <c r="R20" t="n">
-        <v>7078461</v>
+        <v>7078478</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2708,22 +2703,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119874310</v>
+        <v>119871122</v>
       </c>
       <c r="B21" t="n">
-        <v>95225</v>
+        <v>90580</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2732,25 +2727,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2760,10 +2755,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577326</v>
+        <v>577641</v>
       </c>
       <c r="R21" t="n">
-        <v>7078610</v>
+        <v>7078334</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2810,19 +2805,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119872658</v>
+        <v>119871920</v>
       </c>
       <c r="B22" t="n">
         <v>90580</v>
@@ -2858,14 +2853,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577509</v>
+        <v>577561</v>
       </c>
       <c r="R22" t="n">
-        <v>7078448</v>
+        <v>7078431</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2892,12 +2887,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,22 +2907,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119872304</v>
+        <v>119873589</v>
       </c>
       <c r="B23" t="n">
-        <v>90580</v>
+        <v>57473</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2940,37 +2935,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577577</v>
+        <v>577449</v>
       </c>
       <c r="R23" t="n">
-        <v>7078356</v>
+        <v>7078490</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2994,12 +2994,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3026,10 +3026,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119873315</v>
+        <v>119871541</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3042,21 +3042,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577459</v>
+        <v>577611</v>
       </c>
       <c r="R24" t="n">
-        <v>7078453</v>
+        <v>7078365</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3128,10 +3128,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119873866</v>
+        <v>119871553</v>
       </c>
       <c r="B25" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3144,21 +3144,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577389</v>
+        <v>577606</v>
       </c>
       <c r="R25" t="n">
-        <v>7078502</v>
+        <v>7078395</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3198,12 +3198,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3218,22 +3218,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119873602</v>
+        <v>119873574</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>79659</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3242,25 +3242,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577440</v>
+        <v>577449</v>
       </c>
       <c r="R26" t="n">
-        <v>7078487</v>
+        <v>7078503</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3320,22 +3320,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119872102</v>
+        <v>119870839</v>
       </c>
       <c r="B27" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3348,37 +3348,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577567</v>
+        <v>577741</v>
       </c>
       <c r="R27" t="n">
-        <v>7078377</v>
+        <v>7078329</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3422,22 +3422,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119871553</v>
+        <v>119872661</v>
       </c>
       <c r="B28" t="n">
-        <v>79623</v>
+        <v>90923</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3446,25 +3446,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>2062</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3474,10 +3474,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577606</v>
+        <v>577523</v>
       </c>
       <c r="R28" t="n">
-        <v>7078395</v>
+        <v>7078418</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3504,12 +3504,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3536,10 +3536,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119871327</v>
+        <v>119872671</v>
       </c>
       <c r="B29" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3552,34 +3552,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577636</v>
+        <v>577506</v>
       </c>
       <c r="R29" t="n">
-        <v>7078360</v>
+        <v>7078431</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3638,10 +3638,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119873251</v>
+        <v>119872658</v>
       </c>
       <c r="B30" t="n">
-        <v>90545</v>
+        <v>90580</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3650,38 +3650,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577491</v>
+        <v>577509</v>
       </c>
       <c r="R30" t="n">
-        <v>7078459</v>
+        <v>7078448</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3740,10 +3740,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119871541</v>
+        <v>119871099</v>
       </c>
       <c r="B31" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3756,34 +3756,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577611</v>
+        <v>577650</v>
       </c>
       <c r="R31" t="n">
-        <v>7078365</v>
+        <v>7078332</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3830,22 +3830,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119873062</v>
+        <v>119873251</v>
       </c>
       <c r="B32" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3854,42 +3854,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577511</v>
+        <v>577491</v>
       </c>
       <c r="R32" t="n">
-        <v>7078434</v>
+        <v>7078459</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3948,10 +3944,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119871000</v>
+        <v>119871269</v>
       </c>
       <c r="B33" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3964,34 +3960,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577653</v>
+        <v>577631</v>
       </c>
       <c r="R33" t="n">
-        <v>7078341</v>
+        <v>7078350</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4038,19 +4034,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119871910</v>
+        <v>119873866</v>
       </c>
       <c r="B34" t="n">
         <v>78542</v>
@@ -4086,14 +4082,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577581</v>
+        <v>577389</v>
       </c>
       <c r="R34" t="n">
-        <v>7078410</v>
+        <v>7078502</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4152,10 +4148,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119873511</v>
+        <v>119873062</v>
       </c>
       <c r="B35" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4164,38 +4160,42 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577445</v>
+        <v>577511</v>
       </c>
       <c r="R35" t="n">
-        <v>7078496</v>
+        <v>7078434</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4242,22 +4242,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119872661</v>
+        <v>119872285</v>
       </c>
       <c r="B36" t="n">
-        <v>90923</v>
+        <v>90864</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4266,38 +4266,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577523</v>
+        <v>577564</v>
       </c>
       <c r="R36" t="n">
-        <v>7078418</v>
+        <v>7078366</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4344,22 +4344,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119871099</v>
+        <v>119873602</v>
       </c>
       <c r="B37" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4372,21 +4372,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4396,10 +4396,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>577650</v>
+        <v>577440</v>
       </c>
       <c r="R37" t="n">
-        <v>7078332</v>
+        <v>7078487</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4458,10 +4458,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119873018</v>
+        <v>119871569</v>
       </c>
       <c r="B38" t="n">
-        <v>90598</v>
+        <v>79652</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4470,25 +4470,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4498,13 +4498,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577513</v>
+        <v>577607</v>
       </c>
       <c r="R38" t="n">
-        <v>7078427</v>
+        <v>7078381</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4528,12 +4528,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4560,10 +4560,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119871920</v>
+        <v>119871910</v>
       </c>
       <c r="B39" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4576,34 +4576,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577561</v>
+        <v>577581</v>
       </c>
       <c r="R39" t="n">
-        <v>7078431</v>
+        <v>7078410</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4630,12 +4630,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4650,19 +4650,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119870839</v>
+        <v>119873315</v>
       </c>
       <c r="B40" t="n">
         <v>78542</v>
@@ -4702,10 +4702,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577741</v>
+        <v>577459</v>
       </c>
       <c r="R40" t="n">
-        <v>7078329</v>
+        <v>7078453</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4764,10 +4764,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119873728</v>
+        <v>119872304</v>
       </c>
       <c r="B41" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4780,21 +4780,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577416</v>
+        <v>577577</v>
       </c>
       <c r="R41" t="n">
-        <v>7078478</v>
+        <v>7078356</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4834,12 +4834,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4854,19 +4854,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119871122</v>
+        <v>119871327</v>
       </c>
       <c r="B42" t="n">
         <v>90580</v>
@@ -4902,14 +4902,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577641</v>
+        <v>577636</v>
       </c>
       <c r="R42" t="n">
-        <v>7078334</v>
+        <v>7078360</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4956,22 +4956,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119871569</v>
+        <v>119873713</v>
       </c>
       <c r="B43" t="n">
-        <v>79652</v>
+        <v>96885</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4984,21 +4984,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5008,13 +5008,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577607</v>
+        <v>577422</v>
       </c>
       <c r="R43" t="n">
-        <v>7078381</v>
+        <v>7078461</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5038,12 +5038,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -2922,7 +2922,7 @@
         <v>119873589</v>
       </c>
       <c r="B23" t="n">
-        <v>57473</v>
+        <v>57522</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2953,11 +2953,14 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tågsjötorp, Tågsjötorp, Ång</t>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -2922,7 +2922,7 @@
         <v>119873589</v>
       </c>
       <c r="B23" t="n">
-        <v>57522</v>
+        <v>57525</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -2922,7 +2922,7 @@
         <v>119873589</v>
       </c>
       <c r="B23" t="n">
-        <v>57525</v>
+        <v>57527</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -2922,7 +2922,7 @@
         <v>119873589</v>
       </c>
       <c r="B23" t="n">
-        <v>57527</v>
+        <v>57532</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -2937,11 +2937,6 @@
       <c r="E23" t="n">
         <v>103021</v>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>Poecile montanus</t>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -2922,7 +2922,7 @@
         <v>119873589</v>
       </c>
       <c r="B23" t="n">
-        <v>57532</v>
+        <v>57536</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2936,6 +2936,11 @@
       </c>
       <c r="E23" t="n">
         <v>103021</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -2922,7 +2922,7 @@
         <v>119873589</v>
       </c>
       <c r="B23" t="n">
-        <v>57536</v>
+        <v>57537</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -5175,10 +5175,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124302454</v>
+        <v>124306240</v>
       </c>
       <c r="B45" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5187,38 +5187,47 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>577576</v>
+        <v>577332</v>
       </c>
       <c r="R45" t="n">
-        <v>7078368</v>
+        <v>7078511</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5277,10 +5286,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124302189</v>
+        <v>124302867</v>
       </c>
       <c r="B46" t="n">
-        <v>57666</v>
+        <v>91012</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5293,21 +5302,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5317,10 +5326,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>577593</v>
+        <v>577548</v>
       </c>
       <c r="R46" t="n">
-        <v>7078347</v>
+        <v>7078387</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5379,7 +5388,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124302821</v>
+        <v>124302189</v>
       </c>
       <c r="B47" t="n">
         <v>57666</v>
@@ -5419,10 +5428,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>577545</v>
+        <v>577593</v>
       </c>
       <c r="R47" t="n">
-        <v>7078395</v>
+        <v>7078347</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5481,10 +5490,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124306240</v>
+        <v>124302821</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5493,47 +5502,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>577332</v>
+        <v>577545</v>
       </c>
       <c r="R48" t="n">
-        <v>7078511</v>
+        <v>7078395</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5592,10 +5592,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124302867</v>
+        <v>124302391</v>
       </c>
       <c r="B49" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5608,21 +5608,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5632,10 +5632,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>577548</v>
+        <v>577581</v>
       </c>
       <c r="R49" t="n">
-        <v>7078387</v>
+        <v>7078375</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5694,10 +5694,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124302391</v>
+        <v>124302454</v>
       </c>
       <c r="B50" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5710,21 +5710,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5734,10 +5734,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>577581</v>
+        <v>577576</v>
       </c>
       <c r="R50" t="n">
-        <v>7078375</v>
+        <v>7078368</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -5175,10 +5175,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124306240</v>
+        <v>124302391</v>
       </c>
       <c r="B45" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5187,47 +5187,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>577332</v>
+        <v>577581</v>
       </c>
       <c r="R45" t="n">
-        <v>7078511</v>
+        <v>7078375</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5286,10 +5277,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124302867</v>
+        <v>124306240</v>
       </c>
       <c r="B46" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5298,38 +5289,47 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>577548</v>
+        <v>577332</v>
       </c>
       <c r="R46" t="n">
-        <v>7078387</v>
+        <v>7078511</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5388,10 +5388,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124302189</v>
+        <v>124302454</v>
       </c>
       <c r="B47" t="n">
-        <v>57666</v>
+        <v>91299</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5404,21 +5404,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5428,10 +5428,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>577593</v>
+        <v>577576</v>
       </c>
       <c r="R47" t="n">
-        <v>7078347</v>
+        <v>7078368</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5490,10 +5490,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124302821</v>
+        <v>124302867</v>
       </c>
       <c r="B48" t="n">
-        <v>57666</v>
+        <v>91012</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5506,21 +5506,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5530,10 +5530,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>577545</v>
+        <v>577548</v>
       </c>
       <c r="R48" t="n">
-        <v>7078395</v>
+        <v>7078387</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5592,10 +5592,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124302391</v>
+        <v>124302189</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5608,21 +5608,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5632,10 +5632,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>577581</v>
+        <v>577593</v>
       </c>
       <c r="R49" t="n">
-        <v>7078375</v>
+        <v>7078347</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5694,10 +5694,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124302454</v>
+        <v>124302821</v>
       </c>
       <c r="B50" t="n">
-        <v>91299</v>
+        <v>57666</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5710,21 +5710,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5734,10 +5734,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>577576</v>
+        <v>577545</v>
       </c>
       <c r="R50" t="n">
-        <v>7078368</v>
+        <v>7078395</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -5175,10 +5175,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124302391</v>
+        <v>124302867</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5191,21 +5191,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5215,10 +5215,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>577581</v>
+        <v>577548</v>
       </c>
       <c r="R45" t="n">
-        <v>7078375</v>
+        <v>7078387</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5277,10 +5277,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124306240</v>
+        <v>124302454</v>
       </c>
       <c r="B46" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5289,47 +5289,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>577332</v>
+        <v>577576</v>
       </c>
       <c r="R46" t="n">
-        <v>7078511</v>
+        <v>7078368</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5388,10 +5379,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124302454</v>
+        <v>124302391</v>
       </c>
       <c r="B47" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5404,21 +5395,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5428,10 +5419,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>577576</v>
+        <v>577581</v>
       </c>
       <c r="R47" t="n">
-        <v>7078368</v>
+        <v>7078375</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5490,10 +5481,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124302867</v>
+        <v>124306240</v>
       </c>
       <c r="B48" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5502,38 +5493,47 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>577548</v>
+        <v>577332</v>
       </c>
       <c r="R48" t="n">
-        <v>7078387</v>
+        <v>7078511</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5592,7 +5592,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124302189</v>
+        <v>124302821</v>
       </c>
       <c r="B49" t="n">
         <v>57666</v>
@@ -5632,10 +5632,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>577593</v>
+        <v>577545</v>
       </c>
       <c r="R49" t="n">
-        <v>7078347</v>
+        <v>7078395</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5694,7 +5694,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124302821</v>
+        <v>124302189</v>
       </c>
       <c r="B50" t="n">
         <v>57666</v>
@@ -5734,10 +5734,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>577545</v>
+        <v>577593</v>
       </c>
       <c r="R50" t="n">
-        <v>7078395</v>
+        <v>7078347</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -5175,10 +5175,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124302867</v>
+        <v>124306240</v>
       </c>
       <c r="B45" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5187,38 +5187,47 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>577548</v>
+        <v>577332</v>
       </c>
       <c r="R45" t="n">
-        <v>7078387</v>
+        <v>7078511</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5277,10 +5286,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124302454</v>
+        <v>124302867</v>
       </c>
       <c r="B46" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5293,21 +5302,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5317,10 +5326,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>577576</v>
+        <v>577548</v>
       </c>
       <c r="R46" t="n">
-        <v>7078368</v>
+        <v>7078387</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5481,10 +5490,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124306240</v>
+        <v>124302454</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5493,47 +5502,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>577332</v>
+        <v>577576</v>
       </c>
       <c r="R48" t="n">
-        <v>7078511</v>
+        <v>7078368</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5592,7 +5592,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124302821</v>
+        <v>124302189</v>
       </c>
       <c r="B49" t="n">
         <v>57666</v>
@@ -5632,10 +5632,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>577545</v>
+        <v>577593</v>
       </c>
       <c r="R49" t="n">
-        <v>7078395</v>
+        <v>7078347</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5694,7 +5694,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124302189</v>
+        <v>124302821</v>
       </c>
       <c r="B50" t="n">
         <v>57666</v>
@@ -5734,10 +5734,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>577593</v>
+        <v>577545</v>
       </c>
       <c r="R50" t="n">
-        <v>7078347</v>
+        <v>7078395</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -5175,10 +5175,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124306240</v>
+        <v>124302454</v>
       </c>
       <c r="B45" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5187,47 +5187,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>577332</v>
+        <v>577576</v>
       </c>
       <c r="R45" t="n">
-        <v>7078511</v>
+        <v>7078368</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5286,10 +5277,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124302867</v>
+        <v>124306240</v>
       </c>
       <c r="B46" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5298,38 +5289,47 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>577548</v>
+        <v>577332</v>
       </c>
       <c r="R46" t="n">
-        <v>7078387</v>
+        <v>7078511</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5388,10 +5388,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124302391</v>
+        <v>124302189</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5404,21 +5404,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5428,10 +5428,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>577581</v>
+        <v>577593</v>
       </c>
       <c r="R47" t="n">
-        <v>7078375</v>
+        <v>7078347</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5490,10 +5490,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124302454</v>
+        <v>124302821</v>
       </c>
       <c r="B48" t="n">
-        <v>91299</v>
+        <v>57666</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5506,21 +5506,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5530,10 +5530,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>577576</v>
+        <v>577545</v>
       </c>
       <c r="R48" t="n">
-        <v>7078368</v>
+        <v>7078395</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5592,10 +5592,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124302189</v>
+        <v>124302391</v>
       </c>
       <c r="B49" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5608,21 +5608,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5632,10 +5632,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>577593</v>
+        <v>577581</v>
       </c>
       <c r="R49" t="n">
-        <v>7078347</v>
+        <v>7078375</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5694,10 +5694,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124302821</v>
+        <v>124302867</v>
       </c>
       <c r="B50" t="n">
-        <v>57666</v>
+        <v>91012</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5710,21 +5710,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5734,10 +5734,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>577545</v>
+        <v>577548</v>
       </c>
       <c r="R50" t="n">
-        <v>7078395</v>
+        <v>7078387</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -5175,10 +5175,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124302454</v>
+        <v>124302821</v>
       </c>
       <c r="B45" t="n">
-        <v>91299</v>
+        <v>57666</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5191,21 +5191,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5215,10 +5215,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>577576</v>
+        <v>577545</v>
       </c>
       <c r="R45" t="n">
-        <v>7078368</v>
+        <v>7078395</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5277,10 +5277,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124306240</v>
+        <v>124302454</v>
       </c>
       <c r="B46" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5289,47 +5289,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>577332</v>
+        <v>577576</v>
       </c>
       <c r="R46" t="n">
-        <v>7078511</v>
+        <v>7078368</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5388,10 +5379,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124302189</v>
+        <v>124302867</v>
       </c>
       <c r="B47" t="n">
-        <v>57666</v>
+        <v>91012</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5404,21 +5395,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5428,10 +5419,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>577593</v>
+        <v>577548</v>
       </c>
       <c r="R47" t="n">
-        <v>7078347</v>
+        <v>7078387</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5490,10 +5481,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124302821</v>
+        <v>124306240</v>
       </c>
       <c r="B48" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5502,38 +5493,47 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>577545</v>
+        <v>577332</v>
       </c>
       <c r="R48" t="n">
-        <v>7078395</v>
+        <v>7078511</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5694,10 +5694,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124302867</v>
+        <v>124302189</v>
       </c>
       <c r="B50" t="n">
-        <v>91012</v>
+        <v>57666</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5710,21 +5710,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5734,10 +5734,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>577548</v>
+        <v>577593</v>
       </c>
       <c r="R50" t="n">
-        <v>7078387</v>
+        <v>7078347</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -5175,10 +5175,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124302821</v>
+        <v>124302391</v>
       </c>
       <c r="B45" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5191,21 +5191,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5215,10 +5215,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>577545</v>
+        <v>577581</v>
       </c>
       <c r="R45" t="n">
-        <v>7078395</v>
+        <v>7078375</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5277,10 +5277,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124302454</v>
+        <v>124302189</v>
       </c>
       <c r="B46" t="n">
-        <v>91299</v>
+        <v>57666</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5293,21 +5293,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>577576</v>
+        <v>577593</v>
       </c>
       <c r="R46" t="n">
-        <v>7078368</v>
+        <v>7078347</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5379,10 +5379,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124302867</v>
+        <v>124306240</v>
       </c>
       <c r="B47" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5391,38 +5391,47 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>577548</v>
+        <v>577332</v>
       </c>
       <c r="R47" t="n">
-        <v>7078387</v>
+        <v>7078511</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5481,10 +5490,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124306240</v>
+        <v>124302821</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5493,47 +5502,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>577332</v>
+        <v>577545</v>
       </c>
       <c r="R48" t="n">
-        <v>7078511</v>
+        <v>7078395</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5592,10 +5592,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124302391</v>
+        <v>124302454</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5608,21 +5608,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5632,10 +5632,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>577581</v>
+        <v>577576</v>
       </c>
       <c r="R49" t="n">
-        <v>7078375</v>
+        <v>7078368</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5694,10 +5694,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124302189</v>
+        <v>124302867</v>
       </c>
       <c r="B50" t="n">
-        <v>57666</v>
+        <v>91012</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5710,21 +5710,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5734,10 +5734,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>577593</v>
+        <v>577548</v>
       </c>
       <c r="R50" t="n">
-        <v>7078347</v>
+        <v>7078387</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -5175,10 +5175,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124302391</v>
+        <v>124302189</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5191,21 +5191,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5215,10 +5215,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>577581</v>
+        <v>577593</v>
       </c>
       <c r="R45" t="n">
-        <v>7078375</v>
+        <v>7078347</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5277,10 +5277,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124302189</v>
+        <v>124302454</v>
       </c>
       <c r="B46" t="n">
-        <v>57666</v>
+        <v>91299</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5293,21 +5293,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>577593</v>
+        <v>577576</v>
       </c>
       <c r="R46" t="n">
-        <v>7078347</v>
+        <v>7078368</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5379,10 +5379,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124306240</v>
+        <v>124302391</v>
       </c>
       <c r="B47" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5391,47 +5391,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>577332</v>
+        <v>577581</v>
       </c>
       <c r="R47" t="n">
-        <v>7078511</v>
+        <v>7078375</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5490,10 +5481,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124302821</v>
+        <v>124306240</v>
       </c>
       <c r="B48" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5502,38 +5493,47 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>577545</v>
+        <v>577332</v>
       </c>
       <c r="R48" t="n">
-        <v>7078395</v>
+        <v>7078511</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5592,10 +5592,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124302454</v>
+        <v>124302821</v>
       </c>
       <c r="B49" t="n">
-        <v>91299</v>
+        <v>57666</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5608,21 +5608,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5632,10 +5632,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>577576</v>
+        <v>577545</v>
       </c>
       <c r="R49" t="n">
-        <v>7078368</v>
+        <v>7078395</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -5175,7 +5175,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124302189</v>
+        <v>124302821</v>
       </c>
       <c r="B45" t="n">
         <v>57666</v>
@@ -5215,10 +5215,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>577593</v>
+        <v>577545</v>
       </c>
       <c r="R45" t="n">
-        <v>7078347</v>
+        <v>7078395</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5379,10 +5379,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124302391</v>
+        <v>124306240</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5391,38 +5391,47 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>577581</v>
+        <v>577332</v>
       </c>
       <c r="R47" t="n">
-        <v>7078375</v>
+        <v>7078511</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5481,10 +5490,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124306240</v>
+        <v>124302189</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5493,47 +5502,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>577332</v>
+        <v>577593</v>
       </c>
       <c r="R48" t="n">
-        <v>7078511</v>
+        <v>7078347</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5592,10 +5592,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124302821</v>
+        <v>124302391</v>
       </c>
       <c r="B49" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5608,21 +5608,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5632,10 +5632,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>577545</v>
+        <v>577581</v>
       </c>
       <c r="R49" t="n">
-        <v>7078395</v>
+        <v>7078375</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -5175,10 +5175,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124302821</v>
+        <v>124302867</v>
       </c>
       <c r="B45" t="n">
-        <v>57666</v>
+        <v>91012</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5191,21 +5191,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5215,10 +5215,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>577545</v>
+        <v>577548</v>
       </c>
       <c r="R45" t="n">
-        <v>7078395</v>
+        <v>7078387</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5277,10 +5277,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124302454</v>
+        <v>124302189</v>
       </c>
       <c r="B46" t="n">
-        <v>91299</v>
+        <v>57666</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5293,21 +5293,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>577576</v>
+        <v>577593</v>
       </c>
       <c r="R46" t="n">
-        <v>7078368</v>
+        <v>7078347</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5379,10 +5379,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124306240</v>
+        <v>124302821</v>
       </c>
       <c r="B47" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5391,47 +5391,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>577332</v>
+        <v>577545</v>
       </c>
       <c r="R47" t="n">
-        <v>7078511</v>
+        <v>7078395</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5490,10 +5481,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124302189</v>
+        <v>124306240</v>
       </c>
       <c r="B48" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5502,38 +5493,47 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>577593</v>
+        <v>577332</v>
       </c>
       <c r="R48" t="n">
-        <v>7078347</v>
+        <v>7078511</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5694,10 +5694,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124302867</v>
+        <v>124302454</v>
       </c>
       <c r="B50" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5710,21 +5710,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5734,10 +5734,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>577548</v>
+        <v>577576</v>
       </c>
       <c r="R50" t="n">
-        <v>7078387</v>
+        <v>7078368</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -5175,10 +5175,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124302867</v>
+        <v>124306240</v>
       </c>
       <c r="B45" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5187,38 +5187,47 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>577548</v>
+        <v>577332</v>
       </c>
       <c r="R45" t="n">
-        <v>7078387</v>
+        <v>7078511</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5379,10 +5388,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124302821</v>
+        <v>124302454</v>
       </c>
       <c r="B47" t="n">
-        <v>57666</v>
+        <v>91299</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5395,21 +5404,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5419,10 +5428,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>577545</v>
+        <v>577576</v>
       </c>
       <c r="R47" t="n">
-        <v>7078395</v>
+        <v>7078368</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5481,10 +5490,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124306240</v>
+        <v>124302821</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5493,47 +5502,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>577332</v>
+        <v>577545</v>
       </c>
       <c r="R48" t="n">
-        <v>7078511</v>
+        <v>7078395</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5592,10 +5592,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124302391</v>
+        <v>124302867</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5608,21 +5608,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5632,10 +5632,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>577581</v>
+        <v>577548</v>
       </c>
       <c r="R49" t="n">
-        <v>7078375</v>
+        <v>7078387</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5694,10 +5694,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124302454</v>
+        <v>124302391</v>
       </c>
       <c r="B50" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5710,21 +5710,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5734,10 +5734,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>577576</v>
+        <v>577581</v>
       </c>
       <c r="R50" t="n">
-        <v>7078368</v>
+        <v>7078375</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AY51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5289,12 +5289,7 @@
         <v>124302189</v>
       </c>
       <c r="B46" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58023</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5320,6 +5315,14 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
@@ -5794,6 +5797,103 @@
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128716003</v>
+      </c>
+      <c r="B51" t="n">
+        <v>58023</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>577604</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7078390</v>
+      </c>
+      <c r="S51" t="n">
+        <v>15</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -6800,48 +6800,57 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133340463</v>
+        <v>133343831</v>
       </c>
       <c r="B61" t="n">
-        <v>80438</v>
+        <v>99130</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>577604</v>
+        <v>577355</v>
       </c>
       <c r="R61" t="n">
-        <v>7078411</v>
+        <v>7078511</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6897,57 +6906,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133343831</v>
+        <v>133340463</v>
       </c>
       <c r="B62" t="n">
-        <v>99130</v>
+        <v>80438</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>577355</v>
+        <v>577604</v>
       </c>
       <c r="R62" t="n">
-        <v>7078511</v>
+        <v>7078411</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -6800,57 +6800,48 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133343831</v>
+        <v>133340463</v>
       </c>
       <c r="B61" t="n">
-        <v>99130</v>
+        <v>80438</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>577355</v>
+        <v>577604</v>
       </c>
       <c r="R61" t="n">
-        <v>7078511</v>
+        <v>7078411</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6906,48 +6897,57 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133340463</v>
+        <v>133343831</v>
       </c>
       <c r="B62" t="n">
-        <v>80438</v>
+        <v>99130</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>577604</v>
+        <v>577355</v>
       </c>
       <c r="R62" t="n">
-        <v>7078411</v>
+        <v>7078511</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -7206,48 +7206,57 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133642794</v>
+        <v>133644414</v>
       </c>
       <c r="B65" t="n">
-        <v>79359</v>
+        <v>99181</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>577380</v>
+        <v>577417</v>
       </c>
       <c r="R65" t="n">
-        <v>7078565</v>
+        <v>7078462</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7303,57 +7312,48 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133644414</v>
+        <v>133642794</v>
       </c>
       <c r="B66" t="n">
-        <v>99181</v>
+        <v>79359</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>577417</v>
+        <v>577380</v>
       </c>
       <c r="R66" t="n">
-        <v>7078462</v>
+        <v>7078565</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -7006,7 +7006,7 @@
         <v>133642938</v>
       </c>
       <c r="B63" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>133660017</v>
       </c>
       <c r="B64" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7206,57 +7206,48 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133644414</v>
+        <v>133642794</v>
       </c>
       <c r="B65" t="n">
-        <v>99181</v>
+        <v>79366</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>577417</v>
+        <v>577380</v>
       </c>
       <c r="R65" t="n">
-        <v>7078462</v>
+        <v>7078565</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7312,48 +7303,57 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133642794</v>
+        <v>133644414</v>
       </c>
       <c r="B66" t="n">
-        <v>79359</v>
+        <v>99188</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>577380</v>
+        <v>577417</v>
       </c>
       <c r="R66" t="n">
-        <v>7078565</v>
+        <v>7078462</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY66"/>
+  <dimension ref="A1:AY86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102368385</v>
+        <v>119870289</v>
       </c>
       <c r="B2" t="n">
-        <v>93868</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2869</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577328.996306123</v>
+        <v>577682</v>
       </c>
       <c r="R2" t="n">
-        <v>7078622.879926953</v>
+        <v>7078391</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102368381</v>
+        <v>119871000</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577350.9007843664</v>
+        <v>577653</v>
       </c>
       <c r="R3" t="n">
-        <v>7078685.256186267</v>
+        <v>7078341</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -857,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,62 +857,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102368384</v>
+        <v>119871033</v>
       </c>
       <c r="B4" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577493.7858434442</v>
+        <v>577647</v>
       </c>
       <c r="R4" t="n">
-        <v>7078468.809726492</v>
+        <v>7078328</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -969,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,62 +954,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102368361</v>
+        <v>119871099</v>
       </c>
       <c r="B5" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577515.5760142826</v>
+        <v>577650</v>
       </c>
       <c r="R5" t="n">
-        <v>7078464.046735908</v>
+        <v>7078332</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1081,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,27 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102368378</v>
+        <v>119872285</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,34 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577390.7011855737</v>
+        <v>577564</v>
       </c>
       <c r="R6" t="n">
-        <v>7078541.80130443</v>
+        <v>7078366</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1193,22 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,27 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>102368380</v>
+        <v>119872671</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,34 +1171,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Ång</t>
+          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577383.6071281106</v>
+        <v>577506</v>
       </c>
       <c r="R7" t="n">
-        <v>7078542.509943748</v>
+        <v>7078431</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1305,22 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,62 +1245,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>102368368</v>
+        <v>124302454</v>
       </c>
       <c r="B8" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577333.4453008642</v>
+        <v>577576</v>
       </c>
       <c r="R8" t="n">
-        <v>7078585.886741028</v>
+        <v>7078368</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1417,22 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,65 +1342,63 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>102368369</v>
+        <v>113360892</v>
       </c>
       <c r="B9" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577333.0505342103</v>
+        <v>577629</v>
       </c>
       <c r="R9" t="n">
-        <v>7078673.774425402</v>
+        <v>7078378</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1529,22 +1422,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,71 +1436,70 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>102368367</v>
+        <v>113361342</v>
       </c>
       <c r="B10" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Ång</t>
+          <t>Tågsjötorp (Backe), Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577391.6178532141</v>
+        <v>577519</v>
       </c>
       <c r="R10" t="n">
-        <v>7078540.498764534</v>
+        <v>7078419</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1641,22 +1523,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1665,33 +1537,29 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113361143</v>
+        <v>119870350</v>
       </c>
       <c r="B11" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,40 +1567,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tågsjötorp (Backe), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577603</v>
+        <v>577686</v>
       </c>
       <c r="R11" t="n">
-        <v>7078386</v>
+        <v>7078384</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1756,12 +1621,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-07-08</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-07-08</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,34 +1635,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113360892</v>
+        <v>119871122</v>
       </c>
       <c r="B12" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1823,22 +1682,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577629</v>
+        <v>577641</v>
       </c>
       <c r="R12" t="n">
-        <v>7078378</v>
+        <v>7078334</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1862,12 +1718,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-07-08</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-07-08</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1876,34 +1732,28 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113361342</v>
+        <v>119871262</v>
       </c>
       <c r="B13" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1929,22 +1779,19 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tågsjötorp (Backe), Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577519</v>
+        <v>577628</v>
       </c>
       <c r="R13" t="n">
-        <v>7078419</v>
+        <v>7078417</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1968,12 +1815,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-07-08</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-07-08</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1982,7 +1829,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2001,15 +1847,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119873018</v>
+        <v>119871327</v>
       </c>
       <c r="B14" t="n">
-        <v>90598</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2017,34 +1858,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577513</v>
+        <v>577636</v>
       </c>
       <c r="R14" t="n">
-        <v>7078427</v>
+        <v>7078360</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2091,27 +1932,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119871000</v>
+        <v>119871541</v>
       </c>
       <c r="B15" t="n">
-        <v>90864</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2119,21 +1955,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2143,10 +1979,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577653</v>
+        <v>577611</v>
       </c>
       <c r="R15" t="n">
-        <v>7078341</v>
+        <v>7078365</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2205,15 +2041,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119873511</v>
+        <v>119871920</v>
       </c>
       <c r="B16" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2221,21 +2052,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2245,10 +2076,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577445</v>
+        <v>577561</v>
       </c>
       <c r="R16" t="n">
-        <v>7078496</v>
+        <v>7078431</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2275,12 +2106,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2307,15 +2138,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119871033</v>
+        <v>119872102</v>
       </c>
       <c r="B17" t="n">
-        <v>90864</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2323,21 +2149,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2347,13 +2173,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577647</v>
+        <v>577567</v>
       </c>
       <c r="R17" t="n">
-        <v>7078328</v>
+        <v>7078377</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2409,15 +2235,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119872102</v>
+        <v>119872304</v>
       </c>
       <c r="B18" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2449,13 +2270,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577567</v>
+        <v>577577</v>
       </c>
       <c r="R18" t="n">
-        <v>7078377</v>
+        <v>7078356</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2479,12 +2300,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2511,50 +2332,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119874310</v>
+        <v>119872658</v>
       </c>
       <c r="B19" t="n">
-        <v>95225</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>577326</v>
+        <v>577509</v>
       </c>
       <c r="R19" t="n">
-        <v>7078610</v>
+        <v>7078448</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2613,15 +2429,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119873728</v>
+        <v>124302867</v>
       </c>
       <c r="B20" t="n">
-        <v>90598</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2629,34 +2440,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577416</v>
+        <v>577548</v>
       </c>
       <c r="R20" t="n">
-        <v>7078478</v>
+        <v>7078387</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2683,12 +2494,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2715,15 +2526,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119871122</v>
+        <v>131932060</v>
       </c>
       <c r="B21" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2751,14 +2557,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577641</v>
+        <v>577576</v>
       </c>
       <c r="R21" t="n">
-        <v>7078334</v>
+        <v>7078373</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2785,12 +2591,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,27 +2611,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119871920</v>
+        <v>119872241</v>
       </c>
       <c r="B22" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2833,21 +2634,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2857,13 +2658,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577561</v>
+        <v>577563</v>
       </c>
       <c r="R22" t="n">
-        <v>7078431</v>
+        <v>7078391</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2887,12 +2688,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2919,61 +2720,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119873589</v>
+        <v>119870519</v>
       </c>
       <c r="B23" t="n">
-        <v>57537</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92281</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>2062</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577449</v>
+        <v>577693</v>
       </c>
       <c r="R23" t="n">
-        <v>7078490</v>
+        <v>7078382</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2997,12 +2785,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,50 +2817,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119871541</v>
+        <v>119872661</v>
       </c>
       <c r="B24" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92281</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577611</v>
+        <v>577523</v>
       </c>
       <c r="R24" t="n">
-        <v>7078365</v>
+        <v>7078418</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3119,62 +2902,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119871553</v>
+        <v>102368361</v>
       </c>
       <c r="B25" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577606</v>
+        <v>577516</v>
       </c>
       <c r="R25" t="n">
-        <v>7078395</v>
+        <v>7078464</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3201,12 +2979,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3221,27 +2999,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119873574</v>
+        <v>119870410</v>
       </c>
       <c r="B26" t="n">
-        <v>79659</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3249,34 +3022,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6464</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577449</v>
+        <v>577692</v>
       </c>
       <c r="R26" t="n">
-        <v>7078503</v>
+        <v>7078377</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3335,37 +3108,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119870839</v>
+        <v>119871879</v>
       </c>
       <c r="B27" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3375,10 +3143,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577741</v>
+        <v>577593</v>
       </c>
       <c r="R27" t="n">
-        <v>7078329</v>
+        <v>7078428</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3437,50 +3205,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119872661</v>
+        <v>119873251</v>
       </c>
       <c r="B28" t="n">
-        <v>90923</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2062</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577523</v>
+        <v>577491</v>
       </c>
       <c r="R28" t="n">
-        <v>7078418</v>
+        <v>7078459</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3527,62 +3290,57 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119872671</v>
+        <v>102368377</v>
       </c>
       <c r="B29" t="n">
-        <v>90864</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
+          <t>Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577506</v>
+        <v>577532</v>
       </c>
       <c r="R29" t="n">
-        <v>7078431</v>
+        <v>7078477</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3609,12 +3367,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3629,62 +3387,57 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119872658</v>
+        <v>102368378</v>
       </c>
       <c r="B30" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
+          <t>Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577509</v>
+        <v>577391</v>
       </c>
       <c r="R30" t="n">
-        <v>7078448</v>
+        <v>7078542</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3711,12 +3464,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3731,62 +3484,57 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119871099</v>
+        <v>102368380</v>
       </c>
       <c r="B31" t="n">
-        <v>90864</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577650</v>
+        <v>577384</v>
       </c>
       <c r="R31" t="n">
-        <v>7078332</v>
+        <v>7078543</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3813,12 +3561,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3833,49 +3581,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119873251</v>
+        <v>119870839</v>
       </c>
       <c r="B32" t="n">
-        <v>90545</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3885,10 +3628,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577491</v>
+        <v>577741</v>
       </c>
       <c r="R32" t="n">
-        <v>7078459</v>
+        <v>7078329</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3950,16 +3693,11 @@
         <v>119871269</v>
       </c>
       <c r="B33" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -4049,19 +3787,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119873866</v>
+        <v>119871466</v>
       </c>
       <c r="B34" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4085,14 +3818,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577389</v>
+        <v>577614</v>
       </c>
       <c r="R34" t="n">
-        <v>7078502</v>
+        <v>7078408</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4151,15 +3884,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119873062</v>
+        <v>119871910</v>
       </c>
       <c r="B35" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4167,38 +3895,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577511</v>
+        <v>577581</v>
       </c>
       <c r="R35" t="n">
-        <v>7078434</v>
+        <v>7078410</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4257,53 +3981,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119872285</v>
+        <v>119871949</v>
       </c>
       <c r="B36" t="n">
-        <v>90864</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577564</v>
+        <v>577573</v>
       </c>
       <c r="R36" t="n">
-        <v>7078366</v>
+        <v>7078427</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4347,31 +4066,26 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119873602</v>
+        <v>119872160</v>
       </c>
       <c r="B37" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4395,14 +4109,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>577440</v>
+        <v>577587</v>
       </c>
       <c r="R37" t="n">
-        <v>7078487</v>
+        <v>7078423</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4449,65 +4163,60 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119871569</v>
+        <v>119873315</v>
       </c>
       <c r="B38" t="n">
-        <v>79652</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577607</v>
+        <v>577459</v>
       </c>
       <c r="R38" t="n">
-        <v>7078381</v>
+        <v>7078453</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4531,12 +4240,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4551,31 +4260,26 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119871910</v>
+        <v>119873602</v>
       </c>
       <c r="B39" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4599,14 +4303,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577581</v>
+        <v>577440</v>
       </c>
       <c r="R39" t="n">
-        <v>7078410</v>
+        <v>7078487</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4653,31 +4357,26 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119873315</v>
+        <v>119873866</v>
       </c>
       <c r="B40" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -4701,14 +4400,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577459</v>
+        <v>577389</v>
       </c>
       <c r="R40" t="n">
-        <v>7078453</v>
+        <v>7078502</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4767,50 +4466,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119872304</v>
+        <v>124302391</v>
       </c>
       <c r="B41" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577577</v>
+        <v>577581</v>
       </c>
       <c r="R41" t="n">
-        <v>7078356</v>
+        <v>7078375</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4837,12 +4531,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4857,65 +4551,60 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119871327</v>
+        <v>132083264</v>
       </c>
       <c r="B42" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577636</v>
+        <v>577629</v>
       </c>
       <c r="R42" t="n">
-        <v>7078360</v>
+        <v>7078378</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4939,12 +4628,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4971,53 +4660,55 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119873713</v>
+        <v>103288904</v>
       </c>
       <c r="B43" t="n">
-        <v>96885</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577422</v>
+        <v>577488</v>
       </c>
       <c r="R43" t="n">
-        <v>7078461</v>
+        <v>7078506</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5041,12 +4732,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5055,71 +4746,70 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119872241</v>
+        <v>103288957</v>
       </c>
       <c r="B44" t="n">
-        <v>91023</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>577563</v>
+        <v>577470</v>
       </c>
       <c r="R44" t="n">
-        <v>7078391</v>
+        <v>7078506</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5143,12 +4833,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5157,80 +4847,70 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124306240</v>
+        <v>113361143</v>
       </c>
       <c r="B45" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Tågsjötorp (Backe), Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>577332</v>
+        <v>577603</v>
       </c>
       <c r="R45" t="n">
-        <v>7078511</v>
+        <v>7078386</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5254,12 +4934,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2023-07-08</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2023-07-08</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5268,6 +4948,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5286,10 +4967,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124302189</v>
+        <v>113361358</v>
       </c>
       <c r="B46" t="n">
-        <v>58043</v>
+        <v>80432</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5297,45 +4978,40 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp (Backe), Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>577593</v>
+        <v>577486</v>
       </c>
       <c r="R46" t="n">
-        <v>7078347</v>
+        <v>7078499</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5359,12 +5035,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2023-07-08</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2023-07-08</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5373,6 +5049,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5391,15 +5068,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124302454</v>
+        <v>119871553</v>
       </c>
       <c r="B47" t="n">
-        <v>91299</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5407,34 +5079,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>577576</v>
+        <v>577606</v>
       </c>
       <c r="R47" t="n">
-        <v>7078368</v>
+        <v>7078395</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5461,12 +5133,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5481,27 +5153,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124302821</v>
+        <v>119873378</v>
       </c>
       <c r="B48" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5509,34 +5176,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>577545</v>
+        <v>577458</v>
       </c>
       <c r="R48" t="n">
-        <v>7078395</v>
+        <v>7078517</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5563,12 +5230,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5595,15 +5262,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124302867</v>
+        <v>119873387</v>
       </c>
       <c r="B49" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5611,34 +5273,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>577548</v>
+        <v>577493</v>
       </c>
       <c r="R49" t="n">
-        <v>7078387</v>
+        <v>7078500</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5665,12 +5327,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5685,27 +5347,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124302391</v>
+        <v>119873511</v>
       </c>
       <c r="B50" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5713,34 +5370,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>577581</v>
+        <v>577445</v>
       </c>
       <c r="R50" t="n">
-        <v>7078375</v>
+        <v>7078496</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5767,12 +5424,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5787,22 +5444,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128716003</v>
+        <v>132082177</v>
       </c>
       <c r="B51" t="n">
-        <v>58043</v>
+        <v>80488</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5810,21 +5467,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5834,10 +5491,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>577604</v>
+        <v>577695</v>
       </c>
       <c r="R51" t="n">
-        <v>7078390</v>
+        <v>7078339</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5864,12 +5521,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5896,10 +5553,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131932060</v>
+        <v>133340463</v>
       </c>
       <c r="B52" t="n">
-        <v>91908</v>
+        <v>80488</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5907,21 +5564,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5931,13 +5588,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>577576</v>
+        <v>577604</v>
       </c>
       <c r="R52" t="n">
-        <v>7078373</v>
+        <v>7078411</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5961,12 +5618,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5993,48 +5650,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132015650</v>
+        <v>119871569</v>
       </c>
       <c r="B53" t="n">
-        <v>58114</v>
+        <v>80461</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>577574</v>
+        <v>577607</v>
       </c>
       <c r="R53" t="n">
-        <v>7078371</v>
+        <v>7078381</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6058,12 +5715,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6078,66 +5735,57 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132066484</v>
+        <v>119873574</v>
       </c>
       <c r="B54" t="n">
-        <v>99119</v>
+        <v>80468</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>577488</v>
+        <v>577449</v>
       </c>
       <c r="R54" t="n">
-        <v>7078442</v>
+        <v>7078503</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6164,12 +5812,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6196,10 +5844,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132082177</v>
+        <v>132087575</v>
       </c>
       <c r="B55" t="n">
-        <v>80433</v>
+        <v>57975</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6207,37 +5855,47 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>577695</v>
+        <v>577569</v>
       </c>
       <c r="R55" t="n">
-        <v>7078339</v>
+        <v>7078456</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6267,6 +5925,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>FÄRSK ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6293,10 +5956,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132084029</v>
+        <v>119873589</v>
       </c>
       <c r="B56" t="n">
-        <v>58115</v>
+        <v>58114</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6321,24 +5984,28 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>togsjön, togsjön, Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>577542</v>
+        <v>577449</v>
       </c>
       <c r="R56" t="n">
-        <v>7078438</v>
+        <v>7078490</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6362,12 +6029,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6382,22 +6049,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132082304</v>
+        <v>124302189</v>
       </c>
       <c r="B57" t="n">
-        <v>58115</v>
+        <v>58114</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6423,16 +6090,24 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>577692</v>
+        <v>577593</v>
       </c>
       <c r="R57" t="n">
-        <v>7078320</v>
+        <v>7078347</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6459,12 +6134,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6491,10 +6166,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132083264</v>
+        <v>124302821</v>
       </c>
       <c r="B58" t="n">
-        <v>79328</v>
+        <v>58114</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6502,37 +6177,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>577629</v>
+        <v>577545</v>
       </c>
       <c r="R58" t="n">
-        <v>7078378</v>
+        <v>7078395</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6556,12 +6231,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6588,57 +6263,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133340413</v>
+        <v>128716003</v>
       </c>
       <c r="B59" t="n">
-        <v>99178</v>
+        <v>58114</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>577600</v>
+        <v>577604</v>
       </c>
       <c r="R59" t="n">
-        <v>7078399</v>
+        <v>7078390</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6662,12 +6328,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6694,57 +6360,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133340943</v>
+        <v>132015650</v>
       </c>
       <c r="B60" t="n">
-        <v>99178</v>
+        <v>58136</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>577583</v>
+        <v>577574</v>
       </c>
       <c r="R60" t="n">
-        <v>7078378</v>
+        <v>7078371</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6768,12 +6425,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6800,10 +6457,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133340463</v>
+        <v>132082304</v>
       </c>
       <c r="B61" t="n">
-        <v>80473</v>
+        <v>58136</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6811,21 +6468,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6835,13 +6492,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>577604</v>
+        <v>577692</v>
       </c>
       <c r="R61" t="n">
-        <v>7078411</v>
+        <v>7078320</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6865,12 +6522,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6897,54 +6554,49 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133343831</v>
+        <v>132084029</v>
       </c>
       <c r="B62" t="n">
-        <v>99178</v>
+        <v>58136</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>togsjön, togsjön, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>577355</v>
+        <v>577542</v>
       </c>
       <c r="R62" t="n">
-        <v>7078511</v>
+        <v>7078438</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6971,12 +6623,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7003,48 +6655,48 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133642938</v>
+        <v>102368384</v>
       </c>
       <c r="B63" t="n">
-        <v>79366</v>
+        <v>99035</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>577389</v>
+        <v>577494</v>
       </c>
       <c r="R63" t="n">
-        <v>7078551</v>
+        <v>7078469</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7068,12 +6720,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7088,22 +6740,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133660017</v>
+        <v>102368143</v>
       </c>
       <c r="B64" t="n">
-        <v>99188</v>
+        <v>99118</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7130,7 +6782,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7138,19 +6790,30 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (63.8246, 16.5768), Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>577392</v>
+        <v>577602</v>
       </c>
       <c r="R64" t="n">
-        <v>7078549</v>
+        <v>7078427</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7174,12 +6837,17 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>3 plants with flower buds. 1 plant with leaves only.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7188,66 +6856,83 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Loïs Rancilhac</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Loïs Rancilhac, Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133642794</v>
+        <v>102368181</v>
       </c>
       <c r="B65" t="n">
-        <v>79366</v>
+        <v>99118</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>577380</v>
+        <v>577673</v>
       </c>
       <c r="R65" t="n">
-        <v>7078565</v>
+        <v>7078406</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7271,12 +6956,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7285,6 +6970,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7303,10 +6989,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133644414</v>
+        <v>119871836</v>
       </c>
       <c r="B66" t="n">
-        <v>99188</v>
+        <v>99118</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7336,24 +7022,19 @@
           <t>100</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>577417</v>
+        <v>577614</v>
       </c>
       <c r="R66" t="n">
-        <v>7078462</v>
+        <v>7078416</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7377,12 +7058,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7397,15 +7078,2031 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>119871885</v>
+      </c>
+      <c r="B67" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>577588</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7078435</v>
+      </c>
+      <c r="S67" t="n">
+        <v>15</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>119873062</v>
+      </c>
+      <c r="B68" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>577511</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7078434</v>
+      </c>
+      <c r="S68" t="n">
+        <v>15</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>124306240</v>
+      </c>
+      <c r="B69" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>577332</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7078511</v>
+      </c>
+      <c r="S69" t="n">
+        <v>15</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>132066484</v>
+      </c>
+      <c r="B70" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>577488</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7078442</v>
+      </c>
+      <c r="S70" t="n">
+        <v>15</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>133340413</v>
+      </c>
+      <c r="B71" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>577600</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7078399</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>133340943</v>
+      </c>
+      <c r="B72" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>577583</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7078378</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>133343831</v>
+      </c>
+      <c r="B73" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>577355</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7078511</v>
+      </c>
+      <c r="S73" t="n">
+        <v>15</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>133644414</v>
+      </c>
+      <c r="B74" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Backe (Tågsjön), Ång</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>577417</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7078462</v>
+      </c>
+      <c r="S74" t="n">
+        <v>15</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>119873713</v>
+      </c>
+      <c r="B75" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>577422</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7078461</v>
+      </c>
+      <c r="S75" t="n">
+        <v>15</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>102368367</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>577392</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7078541</v>
+      </c>
+      <c r="S76" t="n">
+        <v>15</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>102368385</v>
+      </c>
+      <c r="B77" t="n">
+        <v>97231</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>577329</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7078623</v>
+      </c>
+      <c r="S77" t="n">
+        <v>15</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>119874310</v>
+      </c>
+      <c r="B78" t="n">
+        <v>97231</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>577326</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7078610</v>
+      </c>
+      <c r="S78" t="n">
+        <v>15</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>102368381</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>577351</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7078685</v>
+      </c>
+      <c r="S79" t="n">
+        <v>15</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>102368383</v>
+      </c>
+      <c r="B80" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>577366</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7078701</v>
+      </c>
+      <c r="S80" t="n">
+        <v>15</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>133642794</v>
+      </c>
+      <c r="B81" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>577380</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7078565</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>133642938</v>
+      </c>
+      <c r="B82" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>577389</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7078551</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>133378044</v>
+      </c>
+      <c r="B83" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>577359</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7078691</v>
+      </c>
+      <c r="S83" t="n">
+        <v>15</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>133660017</v>
+      </c>
+      <c r="B84" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>577392</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7078549</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>102368368</v>
+      </c>
+      <c r="B85" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>577333</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7078586</v>
+      </c>
+      <c r="S85" t="n">
+        <v>15</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>102368369</v>
+      </c>
+      <c r="B86" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>577333</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7078674</v>
+      </c>
+      <c r="S86" t="n">
+        <v>15</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY86"/>
+  <dimension ref="A1:AZ86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119870289</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119871000</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119871033</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119871099</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119872285</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119872671</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124302454</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1452,6 +1492,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113360892</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1553,6 +1598,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113361342</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1650,6 +1700,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119870350</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1747,6 +1802,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119871122</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1844,6 +1904,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119871262</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1941,6 +2006,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119871327</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2038,6 +2108,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119871541</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2135,6 +2210,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119871920</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2232,6 +2312,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119872102</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2329,6 +2414,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119872304</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2426,6 +2516,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119872658</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2523,6 +2618,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124302867</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2620,6 +2720,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131932060</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2717,6 +2822,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119872241</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2814,6 +2924,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119870519</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2911,6 +3026,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119872661</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3008,6 +3128,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368385</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3105,6 +3230,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119874310</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3202,6 +3332,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368361</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3299,6 +3434,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119870410</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3396,6 +3536,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119871879</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3493,6 +3638,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119873251</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3590,6 +3740,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368377</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3687,6 +3842,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368378</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3784,6 +3944,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368380</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3881,6 +4046,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368381</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3978,6 +4148,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368383</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4075,6 +4250,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119870839</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4172,6 +4352,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119871269</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4269,6 +4454,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119871466</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4366,6 +4556,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119871910</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4463,6 +4658,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119871949</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4560,6 +4760,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119872160</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4657,6 +4862,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119873315</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4754,6 +4964,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119873602</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4851,6 +5066,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119873866</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4948,6 +5168,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124302391</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5045,6 +5270,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132083264</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5142,6 +5372,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133642794</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5239,6 +5474,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133642938</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5344,6 +5584,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103288904</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5445,6 +5690,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103288957</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5546,6 +5796,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113361143</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5647,6 +5902,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113361358</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5744,6 +6004,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119871553</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5841,6 +6106,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119873378</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5938,6 +6208,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119873387</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6035,6 +6310,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119873511</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6132,6 +6412,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132082177</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6229,6 +6514,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133340463</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6326,6 +6616,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119871569</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6423,6 +6718,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119873574</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6535,6 +6835,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132087575</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6640,6 +6945,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119873589</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6745,6 +7055,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124302189</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6842,6 +7157,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124302821</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6939,6 +7259,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128716003</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7036,6 +7361,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132015650</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7133,6 +7463,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132082304</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7234,6 +7569,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132084029</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7331,6 +7671,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368384</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7454,6 +7799,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368143</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7568,6 +7918,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368181</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7669,6 +8024,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119871836</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7766,6 +8126,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119871885</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7867,6 +8232,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119873062</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7973,6 +8343,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124306240</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8079,6 +8454,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132066484</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8185,6 +8565,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133340413</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8291,6 +8676,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133340943</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8397,6 +8787,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133343831</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8503,6 +8898,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133378044</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8609,6 +9009,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133644414</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8715,6 +9120,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133660017</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8812,6 +9222,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119873713</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8909,6 +9324,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368367</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9006,6 +9426,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368368</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9103,8 +9528,100 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368369</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ86"/>
+  <dimension ref="A1:AZ88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7577,45 +7577,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>102368384</v>
+        <v>135642628</v>
       </c>
       <c r="B69" t="n">
-        <v>99035</v>
+        <v>58141</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>577494</v>
+        <v>577353</v>
       </c>
       <c r="R69" t="n">
-        <v>7078469</v>
+        <v>7078642</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7642,12 +7642,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7662,85 +7662,65 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102368384</t>
+          <t>https://artportalen.se/Sighting/135642628</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>102368143</v>
+        <v>102368384</v>
       </c>
       <c r="B70" t="n">
-        <v>99118</v>
+        <v>99035</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr"/>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Backe (63.8246, 16.5768), Ång</t>
+          <t>Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>577602</v>
+        <v>577494</v>
       </c>
       <c r="R70" t="n">
-        <v>7078427</v>
+        <v>7078469</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7764,17 +7744,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>3 plants with flower buds. 1 plant with leaves only.</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7783,31 +7758,30 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Loïs Rancilhac</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Loïs Rancilhac, Michaela Ehmann</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102368143</t>
+          <t>https://artportalen.se/Sighting/102368384</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>102368181</v>
+        <v>102368143</v>
       </c>
       <c r="B71" t="n">
         <v>99118</v>
@@ -7837,7 +7811,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7851,17 +7825,21 @@
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Ång</t>
+          <t>Backe (63.8246, 16.5768), Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>577673</v>
+        <v>577602</v>
       </c>
       <c r="R71" t="n">
-        <v>7078406</v>
+        <v>7078427</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7896,6 +7874,11 @@
           <t>2022-07-19</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>3 plants with flower buds. 1 plant with leaves only.</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -7909,24 +7892,24 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Loïs Rancilhac</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Loïs Rancilhac, Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102368181</t>
+          <t>https://artportalen.se/Sighting/102368143</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119871836</v>
+        <v>102368181</v>
       </c>
       <c r="B72" t="n">
         <v>99118</v>
@@ -7956,22 +7939,34 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>577614</v>
+        <v>577673</v>
       </c>
       <c r="R72" t="n">
-        <v>7078416</v>
+        <v>7078406</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7995,12 +7990,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8009,30 +8004,31 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119871836</t>
+          <t>https://artportalen.se/Sighting/102368181</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119871885</v>
+        <v>119871836</v>
       </c>
       <c r="B73" t="n">
         <v>99118</v>
@@ -8060,20 +8056,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>577588</v>
+        <v>577614</v>
       </c>
       <c r="R73" t="n">
-        <v>7078435</v>
+        <v>7078416</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8117,24 +8117,24 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119871885</t>
+          <t>https://artportalen.se/Sighting/119871836</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119873062</v>
+        <v>119871885</v>
       </c>
       <c r="B74" t="n">
         <v>99118</v>
@@ -8162,21 +8162,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>577511</v>
+        <v>577588</v>
       </c>
       <c r="R74" t="n">
-        <v>7078434</v>
+        <v>7078435</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8234,13 +8230,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119873062</t>
+          <t>https://artportalen.se/Sighting/119871885</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124306240</v>
+        <v>119873062</v>
       </c>
       <c r="B75" t="n">
         <v>99118</v>
@@ -8270,24 +8266,19 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>577332</v>
+        <v>577511</v>
       </c>
       <c r="R75" t="n">
-        <v>7078511</v>
+        <v>7078434</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8314,12 +8305,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8345,16 +8336,16 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124306240</t>
+          <t>https://artportalen.se/Sighting/119873062</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132066484</v>
+        <v>124306240</v>
       </c>
       <c r="B76" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8381,7 +8372,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -8391,14 +8382,14 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>577488</v>
+        <v>577332</v>
       </c>
       <c r="R76" t="n">
-        <v>7078442</v>
+        <v>7078511</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8425,12 +8416,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8456,13 +8447,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132066484</t>
+          <t>https://artportalen.se/Sighting/124306240</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133340413</v>
+        <v>132066484</v>
       </c>
       <c r="B77" t="n">
         <v>99195</v>
@@ -8492,7 +8483,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -8506,13 +8497,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>577600</v>
+        <v>577488</v>
       </c>
       <c r="R77" t="n">
-        <v>7078399</v>
+        <v>7078442</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8536,12 +8527,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8567,13 +8558,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133340413</t>
+          <t>https://artportalen.se/Sighting/132066484</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133340943</v>
+        <v>133340413</v>
       </c>
       <c r="B78" t="n">
         <v>99195</v>
@@ -8603,7 +8594,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -8617,10 +8608,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>577583</v>
+        <v>577600</v>
       </c>
       <c r="R78" t="n">
-        <v>7078378</v>
+        <v>7078399</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8678,13 +8669,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133340943</t>
+          <t>https://artportalen.se/Sighting/133340413</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133343831</v>
+        <v>133340943</v>
       </c>
       <c r="B79" t="n">
         <v>99195</v>
@@ -8714,7 +8705,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -8724,17 +8715,17 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>577355</v>
+        <v>577583</v>
       </c>
       <c r="R79" t="n">
-        <v>7078511</v>
+        <v>7078378</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8789,13 +8780,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133343831</t>
+          <t>https://artportalen.se/Sighting/133340943</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133378044</v>
+        <v>133343831</v>
       </c>
       <c r="B80" t="n">
         <v>99195</v>
@@ -8825,7 +8816,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -8839,10 +8830,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>577359</v>
+        <v>577355</v>
       </c>
       <c r="R80" t="n">
-        <v>7078691</v>
+        <v>7078511</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8869,12 +8860,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8900,13 +8891,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133378044</t>
+          <t>https://artportalen.se/Sighting/133343831</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133644414</v>
+        <v>133378044</v>
       </c>
       <c r="B81" t="n">
         <v>99195</v>
@@ -8936,7 +8927,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -8946,14 +8937,14 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>577417</v>
+        <v>577359</v>
       </c>
       <c r="R81" t="n">
-        <v>7078462</v>
+        <v>7078691</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8980,12 +8971,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9011,13 +9002,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133644414</t>
+          <t>https://artportalen.se/Sighting/133378044</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133660017</v>
+        <v>133644414</v>
       </c>
       <c r="B82" t="n">
         <v>99195</v>
@@ -9047,7 +9038,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -9057,17 +9048,17 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>577392</v>
+        <v>577417</v>
       </c>
       <c r="R82" t="n">
-        <v>7078549</v>
+        <v>7078462</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9122,54 +9113,63 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133660017</t>
+          <t>https://artportalen.se/Sighting/133644414</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119873713</v>
+        <v>133660017</v>
       </c>
       <c r="B83" t="n">
-        <v>97983</v>
+        <v>99195</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>577422</v>
+        <v>577392</v>
       </c>
       <c r="R83" t="n">
-        <v>7078461</v>
+        <v>7078549</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9193,12 +9193,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9213,65 +9213,74 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119873713</t>
+          <t>https://artportalen.se/Sighting/133660017</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>102368367</v>
+        <v>135644617</v>
       </c>
       <c r="B84" t="n">
-        <v>99140</v>
+        <v>99242</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>577392</v>
+        <v>577401</v>
       </c>
       <c r="R84" t="n">
-        <v>7078541</v>
+        <v>7078525</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9295,12 +9304,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9315,27 +9324,27 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102368367</t>
+          <t>https://artportalen.se/Sighting/135644617</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>102368368</v>
+        <v>119873713</v>
       </c>
       <c r="B85" t="n">
-        <v>99140</v>
+        <v>97983</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9343,34 +9352,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>577333</v>
+        <v>577422</v>
       </c>
       <c r="R85" t="n">
-        <v>7078586</v>
+        <v>7078461</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9397,12 +9406,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9417,24 +9426,24 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102368368</t>
+          <t>https://artportalen.se/Sighting/119873713</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>102368369</v>
+        <v>102368367</v>
       </c>
       <c r="B86" t="n">
         <v>99140</v>
@@ -9469,10 +9478,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>577333</v>
+        <v>577392</v>
       </c>
       <c r="R86" t="n">
-        <v>7078674</v>
+        <v>7078541</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9529,6 +9538,210 @@
       </c>
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368367</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>102368368</v>
+      </c>
+      <c r="B87" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>577333</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7078586</v>
+      </c>
+      <c r="S87" t="n">
+        <v>15</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368368</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>102368369</v>
+      </c>
+      <c r="B88" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>577333</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7078674</v>
+      </c>
+      <c r="S88" t="n">
+        <v>15</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/102368369</t>
         </is>
@@ -9621,6 +9834,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -9233,7 +9233,7 @@
         <v>135644617</v>
       </c>
       <c r="B84" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ86"/>
+  <dimension ref="A1:AZ88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7577,45 +7577,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>102368384</v>
+        <v>135642628</v>
       </c>
       <c r="B69" t="n">
-        <v>99035</v>
+        <v>58141</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>577494</v>
+        <v>577353</v>
       </c>
       <c r="R69" t="n">
-        <v>7078469</v>
+        <v>7078642</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7642,12 +7642,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7662,85 +7662,65 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102368384</t>
+          <t>https://artportalen.se/Sighting/135642628</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>102368143</v>
+        <v>102368384</v>
       </c>
       <c r="B70" t="n">
-        <v>99118</v>
+        <v>99035</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr"/>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Backe (63.8246, 16.5768), Ång</t>
+          <t>Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>577602</v>
+        <v>577494</v>
       </c>
       <c r="R70" t="n">
-        <v>7078427</v>
+        <v>7078469</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7764,17 +7744,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>3 plants with flower buds. 1 plant with leaves only.</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7783,31 +7758,30 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Loïs Rancilhac</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Loïs Rancilhac, Michaela Ehmann</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102368143</t>
+          <t>https://artportalen.se/Sighting/102368384</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>102368181</v>
+        <v>102368143</v>
       </c>
       <c r="B71" t="n">
         <v>99118</v>
@@ -7837,7 +7811,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7851,17 +7825,21 @@
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Ång</t>
+          <t>Backe (63.8246, 16.5768), Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>577673</v>
+        <v>577602</v>
       </c>
       <c r="R71" t="n">
-        <v>7078406</v>
+        <v>7078427</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7896,6 +7874,11 @@
           <t>2022-07-19</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>3 plants with flower buds. 1 plant with leaves only.</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -7909,24 +7892,24 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Loïs Rancilhac</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Loïs Rancilhac, Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102368181</t>
+          <t>https://artportalen.se/Sighting/102368143</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119871836</v>
+        <v>102368181</v>
       </c>
       <c r="B72" t="n">
         <v>99118</v>
@@ -7956,22 +7939,34 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>577614</v>
+        <v>577673</v>
       </c>
       <c r="R72" t="n">
-        <v>7078416</v>
+        <v>7078406</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7995,12 +7990,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8009,30 +8004,31 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119871836</t>
+          <t>https://artportalen.se/Sighting/102368181</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119871885</v>
+        <v>119871836</v>
       </c>
       <c r="B73" t="n">
         <v>99118</v>
@@ -8060,20 +8056,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>577588</v>
+        <v>577614</v>
       </c>
       <c r="R73" t="n">
-        <v>7078435</v>
+        <v>7078416</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8117,24 +8117,24 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119871885</t>
+          <t>https://artportalen.se/Sighting/119871836</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119873062</v>
+        <v>119871885</v>
       </c>
       <c r="B74" t="n">
         <v>99118</v>
@@ -8162,21 +8162,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>577511</v>
+        <v>577588</v>
       </c>
       <c r="R74" t="n">
-        <v>7078434</v>
+        <v>7078435</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8234,13 +8230,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119873062</t>
+          <t>https://artportalen.se/Sighting/119871885</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124306240</v>
+        <v>119873062</v>
       </c>
       <c r="B75" t="n">
         <v>99118</v>
@@ -8270,24 +8266,19 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Tågsjötorp (Backe), Tågsjötorp (Backe), Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>577332</v>
+        <v>577511</v>
       </c>
       <c r="R75" t="n">
-        <v>7078511</v>
+        <v>7078434</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8314,12 +8305,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8345,16 +8336,16 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124306240</t>
+          <t>https://artportalen.se/Sighting/119873062</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132066484</v>
+        <v>124306240</v>
       </c>
       <c r="B76" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8381,7 +8372,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -8391,14 +8382,14 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>577488</v>
+        <v>577332</v>
       </c>
       <c r="R76" t="n">
-        <v>7078442</v>
+        <v>7078511</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8425,12 +8416,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8456,13 +8447,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132066484</t>
+          <t>https://artportalen.se/Sighting/124306240</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133340413</v>
+        <v>132066484</v>
       </c>
       <c r="B77" t="n">
         <v>99195</v>
@@ -8492,7 +8483,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -8506,13 +8497,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>577600</v>
+        <v>577488</v>
       </c>
       <c r="R77" t="n">
-        <v>7078399</v>
+        <v>7078442</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8536,12 +8527,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8567,13 +8558,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133340413</t>
+          <t>https://artportalen.se/Sighting/132066484</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133340943</v>
+        <v>133340413</v>
       </c>
       <c r="B78" t="n">
         <v>99195</v>
@@ -8603,7 +8594,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -8617,10 +8608,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>577583</v>
+        <v>577600</v>
       </c>
       <c r="R78" t="n">
-        <v>7078378</v>
+        <v>7078399</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8678,13 +8669,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133340943</t>
+          <t>https://artportalen.se/Sighting/133340413</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133343831</v>
+        <v>133340943</v>
       </c>
       <c r="B79" t="n">
         <v>99195</v>
@@ -8714,7 +8705,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -8724,17 +8715,17 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>577355</v>
+        <v>577583</v>
       </c>
       <c r="R79" t="n">
-        <v>7078511</v>
+        <v>7078378</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8789,13 +8780,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133343831</t>
+          <t>https://artportalen.se/Sighting/133340943</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133378044</v>
+        <v>133343831</v>
       </c>
       <c r="B80" t="n">
         <v>99195</v>
@@ -8825,7 +8816,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -8839,10 +8830,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>577359</v>
+        <v>577355</v>
       </c>
       <c r="R80" t="n">
-        <v>7078691</v>
+        <v>7078511</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8869,12 +8860,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8900,13 +8891,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133378044</t>
+          <t>https://artportalen.se/Sighting/133343831</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133644414</v>
+        <v>133378044</v>
       </c>
       <c r="B81" t="n">
         <v>99195</v>
@@ -8936,7 +8927,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -8946,14 +8937,14 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>577417</v>
+        <v>577359</v>
       </c>
       <c r="R81" t="n">
-        <v>7078462</v>
+        <v>7078691</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8980,12 +8971,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9011,13 +9002,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133644414</t>
+          <t>https://artportalen.se/Sighting/133378044</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133660017</v>
+        <v>133644414</v>
       </c>
       <c r="B82" t="n">
         <v>99195</v>
@@ -9047,7 +9038,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -9057,17 +9048,17 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>577392</v>
+        <v>577417</v>
       </c>
       <c r="R82" t="n">
-        <v>7078549</v>
+        <v>7078462</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9122,54 +9113,63 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133660017</t>
+          <t>https://artportalen.se/Sighting/133644414</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119873713</v>
+        <v>133660017</v>
       </c>
       <c r="B83" t="n">
-        <v>97983</v>
+        <v>99195</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>577422</v>
+        <v>577392</v>
       </c>
       <c r="R83" t="n">
-        <v>7078461</v>
+        <v>7078549</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9193,12 +9193,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9213,65 +9213,74 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119873713</t>
+          <t>https://artportalen.se/Sighting/133660017</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>102368367</v>
+        <v>135644617</v>
       </c>
       <c r="B84" t="n">
-        <v>99140</v>
+        <v>99274</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>577392</v>
+        <v>577401</v>
       </c>
       <c r="R84" t="n">
-        <v>7078541</v>
+        <v>7078525</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9295,12 +9304,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9315,27 +9324,27 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102368367</t>
+          <t>https://artportalen.se/Sighting/135644617</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>102368368</v>
+        <v>119873713</v>
       </c>
       <c r="B85" t="n">
-        <v>99140</v>
+        <v>97983</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9343,34 +9352,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>577333</v>
+        <v>577422</v>
       </c>
       <c r="R85" t="n">
-        <v>7078586</v>
+        <v>7078461</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9397,12 +9406,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9417,24 +9426,24 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102368368</t>
+          <t>https://artportalen.se/Sighting/119873713</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>102368369</v>
+        <v>102368367</v>
       </c>
       <c r="B86" t="n">
         <v>99140</v>
@@ -9469,10 +9478,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>577333</v>
+        <v>577392</v>
       </c>
       <c r="R86" t="n">
-        <v>7078674</v>
+        <v>7078541</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9529,6 +9538,210 @@
       </c>
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368367</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>102368368</v>
+      </c>
+      <c r="B87" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>577333</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7078586</v>
+      </c>
+      <c r="S87" t="n">
+        <v>15</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368368</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>102368369</v>
+      </c>
+      <c r="B88" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>577333</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7078674</v>
+      </c>
+      <c r="S88" t="n">
+        <v>15</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/102368369</t>
         </is>
@@ -9621,6 +9834,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -9233,7 +9233,7 @@
         <v>135644617</v>
       </c>
       <c r="B84" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ88"/>
+  <dimension ref="A1:AZ89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9341,45 +9341,54 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119873713</v>
+        <v>135951509</v>
       </c>
       <c r="B85" t="n">
-        <v>97983</v>
+        <v>99276</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Tågsjötorp, Ång</t>
+          <t>Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>577422</v>
+        <v>577347</v>
       </c>
       <c r="R85" t="n">
-        <v>7078461</v>
+        <v>7078675</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9406,12 +9415,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9426,27 +9435,27 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119873713</t>
+          <t>https://artportalen.se/Sighting/135951509</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>102368367</v>
+        <v>119873713</v>
       </c>
       <c r="B86" t="n">
-        <v>99140</v>
+        <v>97983</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9454,34 +9463,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Tågsjötorp, Ång</t>
+          <t>Tågsjötorp, Tågsjötorp, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>577392</v>
+        <v>577422</v>
       </c>
       <c r="R86" t="n">
-        <v>7078541</v>
+        <v>7078461</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9508,12 +9517,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9528,24 +9537,24 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102368367</t>
+          <t>https://artportalen.se/Sighting/119873713</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>102368368</v>
+        <v>102368367</v>
       </c>
       <c r="B87" t="n">
         <v>99140</v>
@@ -9580,10 +9589,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>577333</v>
+        <v>577392</v>
       </c>
       <c r="R87" t="n">
-        <v>7078586</v>
+        <v>7078541</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9641,13 +9650,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102368368</t>
+          <t>https://artportalen.se/Sighting/102368367</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>102368369</v>
+        <v>102368368</v>
       </c>
       <c r="B88" t="n">
         <v>99140</v>
@@ -9685,7 +9694,7 @@
         <v>577333</v>
       </c>
       <c r="R88" t="n">
-        <v>7078674</v>
+        <v>7078586</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -9742,6 +9751,108 @@
       </c>
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102368368</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>102368369</v>
+      </c>
+      <c r="B89" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Tågsjötorp, Ång</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>577333</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7078674</v>
+      </c>
+      <c r="S89" t="n">
+        <v>15</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/102368369</t>
         </is>
@@ -9836,6 +9947,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -7580,7 +7580,7 @@
         <v>135642628</v>
       </c>
       <c r="B69" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
         <v>135644617</v>
       </c>
       <c r="B84" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>135951509</v>
       </c>
       <c r="B85" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -9233,7 +9233,7 @@
         <v>135644617</v>
       </c>
       <c r="B84" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>135951509</v>
       </c>
       <c r="B85" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -9233,7 +9233,7 @@
         <v>135644617</v>
       </c>
       <c r="B84" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>135951509</v>
       </c>
       <c r="B85" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -7580,7 +7580,7 @@
         <v>135642628</v>
       </c>
       <c r="B69" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
         <v>135644617</v>
       </c>
       <c r="B84" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>135951509</v>
       </c>
       <c r="B85" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -7580,7 +7580,7 @@
         <v>135642628</v>
       </c>
       <c r="B69" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
         <v>135644617</v>
       </c>
       <c r="B84" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>135951509</v>
       </c>
       <c r="B85" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -9344,7 +9344,7 @@
         <v>135951509</v>
       </c>
       <c r="B85" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -9344,7 +9344,7 @@
         <v>135951509</v>
       </c>
       <c r="B85" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -9344,7 +9344,7 @@
         <v>135951509</v>
       </c>
       <c r="B85" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -9344,7 +9344,7 @@
         <v>135951509</v>
       </c>
       <c r="B85" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -9344,7 +9344,7 @@
         <v>135951509</v>
       </c>
       <c r="B85" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 26657-2022 artfynd.xlsx
+++ b/artfynd/A 26657-2022 artfynd.xlsx
@@ -9344,7 +9344,7 @@
         <v>135951509</v>
       </c>
       <c r="B85" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
